--- a/leads.xlsx
+++ b/leads.xlsx
@@ -513,7 +513,7 @@
     <col width="17" customWidth="1" min="38" max="38"/>
     <col width="40" customWidth="1" min="39" max="39"/>
     <col width="40" customWidth="1" min="40" max="40"/>
-    <col width="37" customWidth="1" min="41" max="41"/>
+    <col width="40" customWidth="1" min="41" max="41"/>
     <col width="22" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
@@ -804,7 +804,7 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/917086547703?text=Hi%20from%20Atrya%20Solutions%21%20%0A%0AWe%20help%20CCTV%20companies%20like%20Beast%20Sound%20Installations%20get%20direct%20customers.%20%0A%0AImagine%20capturing%20Google%20leads%20instantly%20with%20a%20professional%20website%20and%201-click%20WhatsApp%20quotes%2C%20instead%20of%20relying%20on%20Justdial%20commissions.%20%0A%0ASee%20a%20DEMO%20of%20what%20we%20customize%20and%20build%20for%20CCTV%20businesses%3A%20https%3A//atryasolutions.netlify.app/%0A%0AWould%20you%20be%20open%20to%20a%2015-minute%20walkthrough%3F</t>
+          <t>https://wa.me/917086547703?text=Hi%20Beast%20Sound%20Installations%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr"/>
@@ -882,24 +882,33 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions! 
-We help CCTV companies like Beast Sound Installations get direct customers. 
-Imagine capturing Google leads instantly with a professional website and 1-click WhatsApp quotes, instead of relying on Justdial commissions. 
-See a DEMO of what we customize and build for CCTV businesses: https://atryasolutions.netlify.app/
-Would you be open to a 15-minute walkthrough?</t>
+          <t>Hi Beast Sound Installations,
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
-          <t>Boost Direct Leads: Beast Sound Installations</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for Beast Sound Installations</t>
         </is>
       </c>
       <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>Hi Beast Sound Installations Team,
-Atrya Solutions builds high-converting websites for CCTV companies. We noticed you're missing an official website, potentially losing direct Google customers to commission-based platforms.
-Our professional sites feature instant 1-click WhatsApp quote buttons, designed to capture leads directly. See a DEMO of what we customize: https://atryasolutions.netlify.app/
-Let's connect for a 15-minute walkthrough to show you how we can help you get more direct enquiries.
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -984,7 +993,7 @@
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/917733893955?text=Hi%20NC%20Security%20System%2C%0A%0AI%20noticed%20you%20don%E2%80%99t%20have%20a%20website%20yet.%20A%20custom%20lead%E2%80%91gen%20site%20with%20instant%201%E2%80%91click%20WhatsApp%20quote%20can%20pull%20Google%20customers%20directly%2C%20saving%20you%20Justdial%20fees.%0A%0ACan%20we%20schedule%20a%2015%E2%80%91min%20walkthrough%20of%20our%20demo%3F%0A%0ABest%2C%0A%5BYour%20Name%5D</t>
+          <t>https://wa.me/917733893955?text=Hi%20NC%20Security%20System%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
         </is>
       </c>
       <c r="R3" s="4" t="inlineStr"/>
@@ -1055,23 +1064,32 @@
       <c r="AM3" s="4" t="inlineStr">
         <is>
           <t>Hi NC Security System,
-I noticed you don’t have a website yet. A custom lead‑gen site with instant 1‑click WhatsApp quote can pull Google customers directly, saving you Justdial fees.
-Can we schedule a 15‑min walkthrough of our demo?
-Best,
-[Your Name]</t>
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN3" s="4" t="inlineStr">
         <is>
-          <t>Get Direct Google Leads, No Website Needed</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for NC Security System</t>
         </is>
       </c>
       <c r="AO3" s="4" t="inlineStr">
         <is>
-          <t>Hi NC Security System,
-I see you currently rely on directories and social media without an official website. That means you’re paying commissions to platforms like Justdial while missing out on direct Google traffic.
-A tailored, SEO‑optimized website with instant 1‑click WhatsApp quote buttons can capture those high‑intent customers and route them straight to you, eliminating third‑party fees.
-We’d love to show you a quick 15‑minute walkthrough of our live demo and discuss how it can boost your lead flow.
+          <t>Hi NC Security System Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1156,7 +1174,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/917735058027?text=Hi%20Protal247%2C%0AI%20noticed%20you%20don%E2%80%99t%20have%20a%20website%2C%20so%20you%E2%80%99re%20likely%20paying%20commissions%20on%20Justdial%20for%20leads.%20We%20build%20high%E2%80%91converting%20lead%E2%80%91gen%20sites%20with%20instant%201%E2%80%91click%20WhatsApp%20quote%20buttons%2C%20driving%20direct%20Google%20customers.%0ACan%20we%20schedule%20a%2015%E2%80%91min%20walkthrough%3F%20Demo%3A%20https%3A//atryasolutions.netlify.app/</t>
+          <t>https://wa.me/917735058027?text=Hi%20Protal247%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr"/>
@@ -1227,21 +1245,32 @@
       <c r="AM4" s="2" t="inlineStr">
         <is>
           <t>Hi Protal247,
-I noticed you don’t have a website, so you’re likely paying commissions on Justdial for leads. We build high‑converting lead‑gen sites with instant 1‑click WhatsApp quote buttons, driving direct Google customers.
-Can we schedule a 15‑min walkthrough? Demo: https://atryasolutions.netlify.app/</t>
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>Stop Paying Lead Commissions</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for Protal247</t>
         </is>
       </c>
       <c r="AO4" s="2" t="inlineStr">
         <is>
-          <t>Hi [Name],
-I see Protal247 currently relies on directories for leads, which means you’re paying commissions on every enquiry. A custom, SEO‑optimized website with a 1‑click WhatsApp quote button can capture direct Google customers, eliminating those fees and boosting conversion rates.
-We’ve built similar solutions for CCTV firms—see our DEMO site (https://atryasolutions.netlify.app/). The platform also integrates a powerful admin panel for job tracking and AMC dispatch, should you need it later.
-Would a 15‑minute walkthrough this week work for you?
+          <t>Hi Protal247 Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1326,7 +1355,7 @@
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/917733457641?text=Hi%20from%20Atrya%20Solutions%21%0A%0AImagine%20getting%20direct%20customer%20calls%20from%20Google%2C%20not%20just%20Justdial.%0A%0AWe%20build%20professional%20websites%20for%20CCTV%20%26%20security%20companies%20like%20yours%20to%20capture%20local%20leads%20directly.%0A%0ABoost%20your%20business%20without%20paying%20commissions.%20Let%27s%20chat%20for%2015%20mins%3F</t>
+          <t>https://wa.me/917733457641?text=Hi%20Premier%20Intercom%20Installation%2C%20Repair%20Services%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
         </is>
       </c>
       <c r="R5" s="4" t="inlineStr"/>
@@ -1396,24 +1425,33 @@
       <c r="AL5" s="4" t="inlineStr"/>
       <c r="AM5" s="4" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions!
-Imagine getting direct customer calls from Google, not just Justdial.
-We build professional websites for CCTV &amp; security companies like yours to capture local leads directly.
-Boost your business without paying commissions. Let's chat for 15 mins?</t>
+          <t>Hi Premier Intercom Installation, Repair Services,
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN5" s="4" t="inlineStr">
         <is>
-          <t>Stop Paying Justdial Commissions?</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for Premier Intercom Installation, Repair Services</t>
         </is>
       </c>
       <c r="AO5" s="4" t="inlineStr">
         <is>
-          <t>Hello Premier Intercom Team,
-Are you tired of relying solely on directories like Justdial and paying high commissions for leads?
-At Atrya Solutions, we specialize in building high-converting websites for CCTV and electronic security companies. Our sites are designed to capture direct customer inquiries from Google, helping you grow your business more profitably.
-See a demo of what we customize and build for businesses like yours: https://atryasolutions.netlify.app/
-Would you be open to a quick 15-minute walkthrough to show you how we can help you get direct customers?
+          <t>Hi Premier Intercom Installation, Repair Services Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1498,7 +1536,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/917085951156?text=Hi%20Video%E2%80%91Comm%2C%0AI%20noticed%20you%20don%E2%80%99t%20have%20a%20website%2C%20so%20you%E2%80%99re%20missing%20direct%20Google%20leads%20and%20paying%20commissions%20on%20directories.%20We%20build%20high%E2%80%91converting%20sites%20with%20instant%201%E2%80%91click%20WhatsApp%20quote%20buttons%20that%20capture%20customers%20instantly.%0ACan%20we%20schedule%20a%2015%E2%80%91min%20walkthrough%3F%20%E2%80%93%20Atrya%20Solutions</t>
+          <t>https://wa.me/917085951156?text=Hi%20Video-Comm%20Security%20Cameras%202%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr"/>
@@ -1568,21 +1606,33 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>Hi Video‑Comm,
-I noticed you don’t have a website, so you’re missing direct Google leads and paying commissions on directories. We build high‑converting sites with instant 1‑click WhatsApp quote buttons that capture customers instantly.
-Can we schedule a 15‑min walkthrough? – Atrya Solutions</t>
+          <t>Hi Video-Comm Security Cameras 2,
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>Capture Direct Google Leads</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for Video-Comm Security Cameras 2</t>
         </is>
       </c>
       <c r="AO6" s="2" t="inlineStr">
         <is>
-          <t>Hi Video‑Comm Security Cameras 2,
-I saw you currently rely on directories and social media without an official website. That means you’re losing direct Google traffic and paying commissions to platforms like Justdial. At Atrya Solutions we create professional lead‑generation websites tailored for CCTV businesses, featuring instant 1‑click WhatsApp quote buttons that turn visitors into qualified leads instantly.
-We’d love to show you a quick 15‑minute walkthrough of our demo and discuss how a custom site can start driving customers straight from Google.
+          <t>Hi Video-Comm Security Cameras 2 Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1667,7 +1717,7 @@
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919178325446?text=Hi%20InstallTech%2C%20I%27m%20%5BYour%20Name%5D%20from%20Atrya%20Solutions.%0A%0AWe%20build%20websites%20specifically%20for%20security%20companies%20like%20yours%20to%20capture%20direct%20customers%20from%20Google.%0A%0AImagine%20getting%20leads%20without%20paying%20commissions%20to%20Justdial%20or%20other%20directories.%20Our%20sites%20feature%20instant%20WhatsApp%20quote%20buttons.%0A%0AWould%20you%20be%20open%20to%20a%20quick%2015-minute%20demo%20of%20what%20we%20customize%20and%20build%3F</t>
+          <t>https://wa.me/919178325446?text=Hi%20InstallTech.%20Security%20Camera%20Systems.%20Data%26Telecom.%20INC%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr"/>
@@ -1737,24 +1787,33 @@
       <c r="AL7" s="4" t="inlineStr"/>
       <c r="AM7" s="4" t="inlineStr">
         <is>
-          <t>Hi InstallTech, I'm [Your Name] from Atrya Solutions.
-We build websites specifically for security companies like yours to capture direct customers from Google.
-Imagine getting leads without paying commissions to Justdial or other directories. Our sites feature instant WhatsApp quote buttons.
-Would you be open to a quick 15-minute demo of what we customize and build?</t>
+          <t>Hi InstallTech. Security Camera Systems. Data&amp;Telecom. INC,
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN7" s="4" t="inlineStr">
         <is>
-          <t>Stop Paying Commissions: Get Direct Leads</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for InstallTech. Security Camera Systems. Data&amp;Telecom. INC</t>
         </is>
       </c>
       <c r="AO7" s="4" t="inlineStr">
         <is>
-          <t>Hi InstallTech Team,
-I noticed you're doing great work, but might be missing out on direct customer leads by not having an official website.
-Atrya Solutions specializes in building high-converting websites for security companies. Our sites help you capture direct customers from Google, reducing reliance on commission-based directories.
-We include features like 1-click WhatsApp quote buttons to boost inquiries.
-Would you be open to a 15-minute walkthrough of a demo we customize and build for businesses like yours?
+          <t>Hi InstallTech. Security Camera Systems. Data&amp;Telecom. INC Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1839,7 +1898,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/918728069753?text=Hi%20%5BName%5D%2C%0AI%E2%80%99m%20from%20Atrya%20Solutions.%20We%20help%20CCTV%20firms%20capture%20direct%20Google%20leads%20with%20a%20high%E2%80%91converting%20website%20and%20instant%201%E2%80%91click%20WhatsApp%20quote%20button%E2%80%94no%20more%20paying%20Justdial%20commissions.%0ACan%20we%20schedule%20a%2015%E2%80%91min%20walkthrough%3F%20Demo%3A%20https%3A//atryasolutions.netlify.app/</t>
+          <t>https://wa.me/918728069753?text=Hi%20Security%20Cameras%20Solutions%20Geek%20Tech%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr"/>
@@ -1909,22 +1968,33 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr">
         <is>
-          <t>Hi [Name],
-I’m from Atrya Solutions. We help CCTV firms capture direct Google leads with a high‑converting website and instant 1‑click WhatsApp quote button—no more paying Justdial commissions.
-Can we schedule a 15‑min walkthrough? Demo: https://atryasolutions.netlify.app/</t>
+          <t>Hi Security Cameras Solutions Geek Tech,
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>Get Direct Google Leads Free</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for Security Cameras Solutions Geek Tech</t>
         </is>
       </c>
       <c r="AO8" s="2" t="inlineStr">
         <is>
-          <t>Hi [First Name],
-I noticed Security Cameras Solutions Geek Tech doesn’t have an official website and relies on directories. That means you’re paying commissions on Justdial and missing out on direct Google customers.
-Atrya Solutions builds professional lead‑generation sites with instant 1‑click WhatsApp quote buttons, driving high‑quality enquiries straight from Google. We’ll handle the design, SEO and integration at no upfront cost, so you capture leads without third‑party fees.
-Would you be open to a 15‑minute walkthrough of our demo and discuss a free custom build? Demo: https://atryasolutions.netlify.app/
+          <t>Hi Security Cameras Solutions Geek Tech Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2068,24 +2138,32 @@
       <c r="AM9" s="4" t="inlineStr">
         <is>
           <t>Hi Chicago Electrical Services,
-Imagine capturing direct Google customers instead of paying commissions.
-We build high-converting websites specifically for CCTV &amp; electronic security companies, featuring instant 1-click WhatsApp quotes.
-See a DEMO of what we customize: https://atryasolutions.netlify.app/
-Would you be open to a quick 15-minute walkthrough?</t>
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN9" s="4" t="inlineStr">
         <is>
-          <t>Boost Leads: Your Direct Website Solution</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for Chicago Electrical Services</t>
         </is>
       </c>
       <c r="AO9" s="4" t="inlineStr">
         <is>
-          <t>Dear Chicago Electrical Services,
-Are you tired of relying solely on directories and paying commissions for leads? We specialize in building professional, lead-generation websites for CCTV and electronic security businesses.
-Our sites feature instant 1-click WhatsApp quote buttons, designed to convert visitors into direct customers.
-See a DEMO of what we customize and build: https://atryasolutions.netlify.app/
-Let's connect for a brief 15-minute walkthrough to show you how we can help you capture more direct business.
+          <t>Hi Chicago Electrical Services Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2170,7 +2248,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/917736374422?text=Hi%20Detect%20All%20Security%2C%0A%0AI%20noticed%20you%20don%E2%80%99t%20have%20a%20website%2C%20so%20you%E2%80%99re%20missing%20direct%20Google%20leads%20and%20paying%20commissions%20on%20Justdial.%20We%20build%20high%E2%80%91converting%20sites%20with%20instant%201%E2%80%91click%20WhatsApp%20quote%20buttons%20%28demo%3A%20https%3A//atryasolutions.netlify.app/%29.%20Can%20we%20schedule%20a%2015%E2%80%91min%20walkthrough%3F%0A%0AReply%20STOP%20and%20I%20won%27t%20contact%20you%20again.</t>
+          <t>https://wa.me/917736374422?text=Hi%20Detect%20All%20Security%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr"/>
@@ -2241,19 +2319,32 @@
       <c r="AM10" s="2" t="inlineStr">
         <is>
           <t>Hi Detect All Security,
-I noticed you don’t have a website, so you’re missing direct Google leads and paying commissions on Justdial. We build high‑converting sites with instant 1‑click WhatsApp quote buttons (demo: https://atryasolutions.netlify.app/). Can we schedule a 15‑min walkthrough?
-Reply STOP and I won't contact you again.</t>
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>Capture Direct Google Leads Today</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for Detect All Security</t>
         </is>
       </c>
       <c r="AO10" s="2" t="inlineStr">
         <is>
-          <t>Hi [First Name],
-I see Detect All Security currently relies on directories and social media, missing out on direct Google traffic and paying commissions on platforms like Justdial. A custom, SEO‑optimized website with instant 1‑click WhatsApp quote buttons can turn searchers into qualified leads instantly. We’ve built similar solutions for CCTV firms—see our demo at https://atryasolutions.netlify.app/. I’d love to walk you through a 15‑minute, no‑obligation demo of how we can boost your lead flow and reduce third‑party costs.
+          <t>Hi Detect All Security Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2393,24 +2484,32 @@
       <c r="AM11" s="4" t="inlineStr">
         <is>
           <t>Hi Electro Alarm Co Inc,
-Are you tired of relying on Justdial or IndiaMART for leads?
-We build professional websites that capture direct Google customers, complete with 1-click WhatsApp quote buttons. Imagine instant inquiries without commissions!
-See a DEMO of what we customize for CCTV businesses: https://atryasolutions.netlify.app/
-Let's chat for 15 mins?</t>
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN11" s="4" t="inlineStr">
         <is>
-          <t>Stop Paying Commissions: Get Direct Leads</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for Electro Alarm Co Inc</t>
         </is>
       </c>
       <c r="AO11" s="4" t="inlineStr">
         <is>
-          <t>Hi Electro Alarm Co Inc,
-Are you looking to capture more direct customers without paying hefty commissions to directories like Justdial?
-We specialize in building high-converting websites for CCTV businesses. Our sites feature instant 1-click WhatsApp quote buttons, designed to turn visitors into leads.
-See a DEMO of what we customize: https://atryasolutions.netlify.app/
-Would you be open to a quick 15-minute walkthrough to show you how we can help you get direct Google customers?
+          <t>Hi Electro Alarm Co Inc Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2487,7 +2586,7 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/917083955335?text=Hi%2C%0AI%20noticed%20DVR%20USA%20Security%20has%20no%20official%20website%2C%20meaning%20you%E2%80%99re%20missing%20direct%20Google%20leads%20and%20still%20paying%20commissions%20on%20directories.%20We%20build%20high%E2%80%91converting%20lead%E2%80%91gen%20sites%20with%20instant%201%E2%80%91click%20WhatsApp%20quote%20buttons.%0ACan%20we%20schedule%20a%2015%E2%80%91minute%20walkthrough%3F%0AReply%20STOP%20to%20opt%E2%80%91out.</t>
+          <t>https://wa.me/917083955335?text=Hi%20DVR%20USA%20Security%20Inc%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr"/>
@@ -2557,26 +2656,33 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr">
         <is>
-          <t>Hi,
-I noticed DVR USA Security has no official website, meaning you’re missing direct Google leads and still paying commissions on directories. We build high‑converting lead‑gen sites with instant 1‑click WhatsApp quote buttons.
-Can we schedule a 15‑minute walkthrough?
-Reply STOP to opt‑out.</t>
+          <t>Hi DVR USA Security Inc,
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>Capture Direct Google Leads Now</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for DVR USA Security Inc</t>
         </is>
       </c>
       <c r="AO12" s="2" t="inlineStr">
         <is>
-          <t>Hello,
-I saw DVR USA Security currently relies only on directories and social media, with no dedicated website. That limits your ability to capture direct Google customers and forces you to pay commissions on platforms like Justdial.
-A professional, SEO‑optimized site with instant 1‑click WhatsApp quote buttons can turn search traffic into qualified leads instantly.
-We’d love to show you a quick 15‑minute walkthrough of a live demo tailored for CCTV businesses.
+          <t>Hi DVR USA Security Inc Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
 Best regards,
-[Your Name]
-Atrya Solutions
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2653,7 +2759,7 @@
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/918154355200?text=Hi%20from%20Atrya%20Solutions%21%0A%0AImagine%20getting%20direct%20customer%20leads%20from%20Google%2C%20instead%20of%20paying%20high%20commissions%20to%20Justdial.%0A%0AWe%20build%20professional%20websites%20with%201-click%20WhatsApp%20quotes%2C%20customized%20for%20CCTV%20businesses.%0A%0ASee%20a%20DEMO%20of%20what%20we%20build%3A%20https%3A//atryasolutions.netlify.app/%0A%0ABook%20a%2015-min%20walkthrough%20to%20see%20how%20we%20can%20help%20Home%20Security%20Direct%20grow.</t>
+          <t>https://wa.me/918154355200?text=Hi%20Home%20Security%20Direct%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr"/>
@@ -2723,26 +2829,33 @@
       <c r="AL13" s="4" t="inlineStr"/>
       <c r="AM13" s="4" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions!
-Imagine getting direct customer leads from Google, instead of paying high commissions to Justdial.
-We build professional websites with 1-click WhatsApp quotes, customized for CCTV businesses.
-See a DEMO of what we build: https://atryasolutions.netlify.app/
-Book a 15-min walkthrough to see how we can help Home Security Direct grow.</t>
+          <t>Hi Home Security Direct,
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN13" s="4" t="inlineStr">
         <is>
-          <t>Stop Paying Justdial Commissions?</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for Home Security Direct</t>
         </is>
       </c>
       <c r="AO13" s="4" t="inlineStr">
         <is>
-          <t>Hello,
-Are you tired of high commissions from Justdial or other directories?
-At Atrya Solutions, we build high-converting websites specifically for CCTV and electronic security companies like Home Security Direct.
-Our sites help you capture direct Google customers with instant 1-click WhatsApp quote buttons.
-See a DEMO of what we customize: https://atryasolutions.netlify.app/
-Would you be open to a quick 15-minute walkthrough to show you how we can boost your direct leads?
+          <t>Hi Home Security Direct Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2827,7 +2940,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/918478092778?text=Hi%20from%20Atrya%20Solutions%21%20%0A%0AWe%20help%20CCTV%20companies%20like%20Top%20Deal%20Trading%20get%20direct%20customers%20from%20Google%2C%20instead%20of%20relying%20on%20Justdial%20or%20social%20media.%20%0A%0AImagine%20a%20professional%20website%20with%20instant%20WhatsApp%20quotes.%20%0A%0ASee%20a%20DEMO%20of%20what%20we%20customize%3A%20https%3A//atryasolutions.netlify.app/%20%0A%0AWould%20you%20be%20open%20to%20a%2015-min%20walkthrough%3F</t>
+          <t>https://wa.me/918478092778?text=Hi%20Top%20Deal%20Trading%20-%20TV%205ALE%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr"/>
@@ -2905,25 +3018,33 @@
       <c r="AL14" s="2" t="inlineStr"/>
       <c r="AM14" s="2" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions! 
-We help CCTV companies like Top Deal Trading get direct customers from Google, instead of relying on Justdial or social media. 
-Imagine a professional website with instant WhatsApp quotes. 
-See a DEMO of what we customize: https://atryasolutions.netlify.app/ 
-Would you be open to a 15-min walkthrough?</t>
+          <t>Hi Top Deal Trading - TV 5ALE,
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>Stop Paying Justdial Commissions?</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for Top Deal Trading - TV 5ALE</t>
         </is>
       </c>
       <c r="AO14" s="2" t="inlineStr">
         <is>
-          <t>Hi Top Deal Trading,
-Are you tired of paying commissions to Justdial or limiting your reach to social media?
-At Atrya Solutions, we build high-converting websites specifically for CCTV companies. Our sites help you capture direct customers from Google with features like instant 1-click WhatsApp quote buttons.
-See a DEMO of what we customize: https://atryasolutions.netlify.app/
-Would you be open to a quick 15-minute walkthrough to show you how we can boost your direct enquiries?
+          <t>Hi Top Deal Trading - TV 5ALE Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3012,7 +3133,7 @@
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/917892328427?text=Hi%20SKYWAY%20INFOSYSTEMS%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%20but%20doesn%27t%20have%20a%20direct%20website.%0AWe%20build%20websites%20and%20technician%20dispatch%20panels%20for%20CCTV%20installers.%0ACheck%20out%20our%20demo%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20for%20a%20quick%2010-min%20demo%3F</t>
+          <t>https://wa.me/917892328427?text=Hi%20SKYWAY%20INFOSYSTEMS%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
         </is>
       </c>
       <c r="R15" s="4" t="inlineStr"/>
@@ -3083,24 +3204,32 @@
       <c r="AM15" s="4" t="inlineStr">
         <is>
           <t>Hi SKYWAY INFOSYSTEMS,
-Noticed your CCTV business in 50 gets great reviews but doesn't have a direct website.
-We build websites and technician dispatch panels for CCTV installers.
-Check out our demo: https://atryasolutions.netlify.app/
-Open for a quick 10-min demo?</t>
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN15" s="4" t="inlineStr">
         <is>
-          <t>Direct website &amp; AMC panel for SKYWAY INFOSYSTEMS</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for SKYWAY INFOSYSTEMS</t>
         </is>
       </c>
       <c r="AO15" s="4" t="inlineStr">
         <is>
-          <t>Hi SKYWAY INFOSYSTEMS,
-I noticed you have strong customer reviews in 50, but potential clients searching Google might not find a direct website to request CCTV quotes.
-At Atrya Solutions, we set up turnkey websites with instant WhatsApp quote buttons and an operations panel to manage AMC maintenance contracts and field technicians.
-Live demo: https://atryasolutions.netlify.app/
-Would you be open to a 10-minute walkthrough this week?
+          <t>Hi SKYWAY INFOSYSTEMS Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3248,24 +3377,32 @@
       <c r="AM16" s="2" t="inlineStr">
         <is>
           <t>Hi Dynamic CCTV Ltd,
-Noticed your CCTV business in 50 gets great reviews but doesn't have a direct website.
-We build websites and technician dispatch panels for CCTV installers.
-Check out our demo: https://atryasolutions.netlify.app/
-Open for a quick 10-min demo?</t>
+Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
+You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week?</t>
         </is>
       </c>
       <c r="AN16" s="2" t="inlineStr">
         <is>
-          <t>Direct website &amp; AMC panel for Dynamic CCTV Ltd</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for Dynamic CCTV Ltd</t>
         </is>
       </c>
       <c r="AO16" s="2" t="inlineStr">
         <is>
-          <t>Hi Dynamic CCTV Ltd,
-I noticed you have strong customer reviews in 50, but potential clients searching Google might not find a direct website to request CCTV quotes.
-At Atrya Solutions, we set up turnkey websites with instant WhatsApp quote buttons and an operations panel to manage AMC maintenance contracts and field technicians.
-Live demo: https://atryasolutions.netlify.app/
-Would you be open to a 10-minute walkthrough this week?
+          <t>Hi Dynamic CCTV Ltd Team,
+I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CCTV Leads" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCTV Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +479,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
@@ -742,7 +742,11 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>cid_3334184614186372508</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>PITCH_DRAFTED</t>
@@ -770,7 +774,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -4129,7 +4133,11 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>cid_13760439922089000441</t>
+        </is>
+      </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>PITCH_DRAFTED</t>
@@ -4157,7 +4165,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4320,7 +4328,11 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="4" t="inlineStr"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>cid_9009305908370015728</t>
+        </is>
+      </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
           <t>PITCH_DRAFTED</t>
@@ -4348,7 +4360,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -5101,7 +5113,11 @@
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="4" t="inlineStr"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>cid_15286622477168565426</t>
+        </is>
+      </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
           <t>PITCH_DRAFTED</t>
@@ -5129,7 +5145,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -5311,7 +5327,11 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>cid_11514133238201629577</t>
+        </is>
+      </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>PITCH_DRAFTED</t>
@@ -5339,7 +5359,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Chintalkunta</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -6119,10 +6139,14 @@
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="2" t="inlineStr"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>cid_17997815080243066282</t>
+        </is>
+      </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -6147,7 +6171,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Keralam</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6271,9 +6295,30 @@
         </is>
       </c>
       <c r="AN30" s="2" t="inlineStr"/>
-      <c r="AO30" s="2" t="inlineStr"/>
-      <c r="AP30" s="2" t="inlineStr"/>
-      <c r="AQ30" s="2" t="inlineStr"/>
+      <c r="AO30" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dahua wiki,
+Took a look at your CCTV website in Keralam and noticed a few things holding back customer enquiries (slow load time (6.0s); no direct WhatsApp contact widget).
+We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+Open to a quick demo?</t>
+        </is>
+      </c>
+      <c r="AP30" s="2" t="inlineStr">
+        <is>
+          <t>Improving CCTV quote enquiries for Dahua wiki</t>
+        </is>
+      </c>
+      <c r="AQ30" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dahua wiki,
+I was looking up CCTV providers in Keralam and checked your website.
+I noticed a couple of areas that might be reducing your lead conversion: slow load time (6.0s); no direct WhatsApp contact widget.
+At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
+Live demo: https://atryasolutions.netlify.app/
+Would you be interested in a brief 10-minute walkthrough?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR30" s="2" t="inlineStr">
         <is>
           <t>2026-10-08 16:39:49</t>
@@ -6288,7 +6333,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -6367,7 +6412,11 @@
           <t>919110421987</t>
         </is>
       </c>
-      <c r="S31" s="4" t="inlineStr"/>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/919110421987?text=Hi%20I%20Pro%20Secure%20CCTV%20CAMERA%20INSTALLATION%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%20Bengaluru%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+        </is>
+      </c>
       <c r="T31" s="4" t="inlineStr"/>
       <c r="U31" s="4" t="inlineStr"/>
       <c r="V31" s="5" t="inlineStr">
@@ -6445,9 +6494,30 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="AO31" s="4" t="inlineStr"/>
-      <c r="AP31" s="4" t="inlineStr"/>
-      <c r="AQ31" s="4" t="inlineStr"/>
+      <c r="AO31" s="4" t="inlineStr">
+        <is>
+          <t>Hi I Pro Secure CCTV CAMERA INSTALLATION,
+Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (no online enquiry or quote form; no direct WhatsApp contact widget).
+We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+Open to a quick demo?</t>
+        </is>
+      </c>
+      <c r="AP31" s="4" t="inlineStr">
+        <is>
+          <t>Improving CCTV quote enquiries for I Pro Secure CCTV CAMERA INSTALLATION</t>
+        </is>
+      </c>
+      <c r="AQ31" s="4" t="inlineStr">
+        <is>
+          <t>Hi I Pro Secure CCTV CAMERA INSTALLATION,
+I was looking up CCTV providers in Bengaluru and checked your website.
+I noticed a couple of areas that might be reducing your lead conversion: no online enquiry or quote form; no direct WhatsApp contact widget.
+At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
+Live demo: https://atryasolutions.netlify.app/
+Would you be interested in a brief 10-minute walkthrough?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR31" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -6462,7 +6532,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -6541,7 +6611,11 @@
           <t>919741427427</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr"/>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/919741427427?text=Hi%20RAMESH%20CCTV%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%20Bengaluru%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+        </is>
+      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
           <t>6399999857; 6999999881; 7606708560</t>
@@ -6623,9 +6697,30 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="AO32" s="2" t="inlineStr"/>
-      <c r="AP32" s="2" t="inlineStr"/>
-      <c r="AQ32" s="2" t="inlineStr"/>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>Hi RAMESH CCTV,
+Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (no online enquiry or quote form; no direct WhatsApp contact widget).
+We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+Open to a quick demo?</t>
+        </is>
+      </c>
+      <c r="AP32" s="2" t="inlineStr">
+        <is>
+          <t>Improving CCTV quote enquiries for RAMESH CCTV</t>
+        </is>
+      </c>
+      <c r="AQ32" s="2" t="inlineStr">
+        <is>
+          <t>Hi RAMESH CCTV,
+I was looking up CCTV providers in Bengaluru and checked your website.
+I noticed a couple of areas that might be reducing your lead conversion: no online enquiry or quote form; no direct WhatsApp contact widget.
+At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
+Live demo: https://atryasolutions.netlify.app/
+Would you be interested in a brief 10-minute walkthrough?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR32" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -6640,7 +6735,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -6719,7 +6814,11 @@
           <t>919035080007</t>
         </is>
       </c>
-      <c r="S33" s="4" t="inlineStr"/>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/919035080007?text=Hi%20SIXAXIS%20CCTV%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%20Bengaluru%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28not%20served%20over%20HTTPS%20%28insecure%20connection%29%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+        </is>
+      </c>
       <c r="T33" s="4" t="inlineStr">
         <is>
           <t>+919035030007</t>
@@ -6821,9 +6920,30 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="AO33" s="4" t="inlineStr"/>
-      <c r="AP33" s="4" t="inlineStr"/>
-      <c r="AQ33" s="4" t="inlineStr"/>
+      <c r="AO33" s="4" t="inlineStr">
+        <is>
+          <t>Hi SIXAXIS CCTV,
+Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (not served over HTTPS (insecure connection)).
+We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+Open to a quick demo?</t>
+        </is>
+      </c>
+      <c r="AP33" s="4" t="inlineStr">
+        <is>
+          <t>Improving CCTV quote enquiries for SIXAXIS CCTV</t>
+        </is>
+      </c>
+      <c r="AQ33" s="4" t="inlineStr">
+        <is>
+          <t>Hi SIXAXIS CCTV,
+I was looking up CCTV providers in Bengaluru and checked your website.
+I noticed a couple of areas that might be reducing your lead conversion: not served over HTTPS (insecure connection).
+At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
+Live demo: https://atryasolutions.netlify.app/
+Would you be interested in a brief 10-minute walkthrough?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR33" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -6838,7 +6958,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -6917,7 +7037,11 @@
           <t>919538380555</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr"/>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/919538380555?text=Hi%20CCTV%20SHOPPING%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%20Bengaluru%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+        </is>
+      </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
           <t>+919538380555; 6395939088; 6666666667</t>
@@ -6999,9 +7123,30 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="AO34" s="2" t="inlineStr"/>
-      <c r="AP34" s="2" t="inlineStr"/>
-      <c r="AQ34" s="2" t="inlineStr"/>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>Hi CCTV SHOPPING,
+Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (no online enquiry or quote form; no direct WhatsApp contact widget).
+We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+Open to a quick demo?</t>
+        </is>
+      </c>
+      <c r="AP34" s="2" t="inlineStr">
+        <is>
+          <t>Improving CCTV quote enquiries for CCTV SHOPPING</t>
+        </is>
+      </c>
+      <c r="AQ34" s="2" t="inlineStr">
+        <is>
+          <t>Hi CCTV SHOPPING,
+I was looking up CCTV providers in Bengaluru and checked your website.
+I noticed a couple of areas that might be reducing your lead conversion: no online enquiry or quote form; no direct WhatsApp contact widget.
+At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
+Live demo: https://atryasolutions.netlify.app/
+Would you be interested in a brief 10-minute walkthrough?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR34" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -7016,7 +7161,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -7095,7 +7240,11 @@
           <t>919739933180</t>
         </is>
       </c>
-      <c r="S35" s="4" t="inlineStr"/>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/919739933180?text=Hi%20KWALITY%20TECH%20ZONE%20LLP%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%20Bengaluru%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+        </is>
+      </c>
       <c r="T35" s="4" t="inlineStr"/>
       <c r="U35" s="4" t="inlineStr"/>
       <c r="V35" s="5" t="inlineStr">
@@ -7169,9 +7318,30 @@
         </is>
       </c>
       <c r="AN35" s="4" t="inlineStr"/>
-      <c r="AO35" s="4" t="inlineStr"/>
-      <c r="AP35" s="4" t="inlineStr"/>
-      <c r="AQ35" s="4" t="inlineStr"/>
+      <c r="AO35" s="4" t="inlineStr">
+        <is>
+          <t>Hi KWALITY TECH ZONE LLP,
+Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (no online enquiry or quote form; no direct WhatsApp contact widget).
+We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+Open to a quick demo?</t>
+        </is>
+      </c>
+      <c r="AP35" s="4" t="inlineStr">
+        <is>
+          <t>Improving CCTV quote enquiries for KWALITY TECH ZONE LLP</t>
+        </is>
+      </c>
+      <c r="AQ35" s="4" t="inlineStr">
+        <is>
+          <t>Hi KWALITY TECH ZONE LLP,
+I was looking up CCTV providers in Bengaluru and checked your website.
+I noticed a couple of areas that might be reducing your lead conversion: no online enquiry or quote form; no direct WhatsApp contact widget.
+At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
+Live demo: https://atryasolutions.netlify.app/
+Would you be interested in a brief 10-minute walkthrough?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR35" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:56</t>
@@ -7186,7 +7356,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -7335,9 +7505,30 @@
         </is>
       </c>
       <c r="AN36" s="2" t="inlineStr"/>
-      <c r="AO36" s="2" t="inlineStr"/>
-      <c r="AP36" s="2" t="inlineStr"/>
-      <c r="AQ36" s="2" t="inlineStr"/>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>Hi Bangalore Electronics,
+Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (no online enquiry or quote form; no direct WhatsApp contact widget).
+We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+Open to a quick demo?</t>
+        </is>
+      </c>
+      <c r="AP36" s="2" t="inlineStr">
+        <is>
+          <t>Improving CCTV quote enquiries for Bangalore Electronics</t>
+        </is>
+      </c>
+      <c r="AQ36" s="2" t="inlineStr">
+        <is>
+          <t>Hi Bangalore Electronics,
+I was looking up CCTV providers in Bengaluru and checked your website.
+I noticed a couple of areas that might be reducing your lead conversion: no online enquiry or quote form; no direct WhatsApp contact widget.
+At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
+Live demo: https://atryasolutions.netlify.app/
+Would you be interested in a brief 10-minute walkthrough?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR36" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:57</t>
@@ -7345,10 +7536,14 @@
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="4" t="inlineStr"/>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>cid_12014290968981143054</t>
+        </is>
+      </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -7373,7 +7568,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -7427,7 +7622,11 @@
           <t>919738966594</t>
         </is>
       </c>
-      <c r="S37" s="4" t="inlineStr"/>
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/919738966594?text=Hi%20Cyber%20Pro%20India%20-%20CCTV%20Installation%20Service%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T37" s="4" t="inlineStr">
         <is>
           <t>+91-9738966594; +919738966594; 6062210545</t>
@@ -7529,9 +7728,29 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="AO37" s="4" t="inlineStr"/>
-      <c r="AP37" s="4" t="inlineStr"/>
-      <c r="AQ37" s="4" t="inlineStr"/>
+      <c r="AO37" s="4" t="inlineStr">
+        <is>
+          <t>Hi Cyber Pro India - CCTV Installation Service,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP37" s="4" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for Cyber Pro India - CCTV Installation Service</t>
+        </is>
+      </c>
+      <c r="AQ37" s="4" t="inlineStr">
+        <is>
+          <t>Hi Cyber Pro India - CCTV Installation Service,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR37" s="4" t="inlineStr">
         <is>
           <t>2026-10-08 16:39:44</t>
@@ -7546,7 +7765,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -7625,7 +7844,11 @@
           <t>919686550099</t>
         </is>
       </c>
-      <c r="S38" s="2" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/919686550099?text=Hi%20Skafoss%20Technologies%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
           <t>+919686550099; 6283185841; 9308893008</t>
@@ -7711,9 +7934,29 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="AO38" s="2" t="inlineStr"/>
-      <c r="AP38" s="2" t="inlineStr"/>
-      <c r="AQ38" s="2" t="inlineStr"/>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>Hi Skafoss Technologies,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP38" s="2" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for Skafoss Technologies</t>
+        </is>
+      </c>
+      <c r="AQ38" s="2" t="inlineStr">
+        <is>
+          <t>Hi Skafoss Technologies,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR38" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -7728,7 +7971,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -7807,7 +8050,11 @@
           <t>919620421001</t>
         </is>
       </c>
-      <c r="S39" s="4" t="inlineStr"/>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/919620421001?text=Hi%20KING%20TECHNOLOGY%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T39" s="4" t="inlineStr">
         <is>
           <t>+919019390194; +919620421001; 6207859085</t>
@@ -7893,9 +8140,29 @@
         </is>
       </c>
       <c r="AN39" s="4" t="inlineStr"/>
-      <c r="AO39" s="4" t="inlineStr"/>
-      <c r="AP39" s="4" t="inlineStr"/>
-      <c r="AQ39" s="4" t="inlineStr"/>
+      <c r="AO39" s="4" t="inlineStr">
+        <is>
+          <t>Hi KING TECHNOLOGY,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP39" s="4" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for KING TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="AQ39" s="4" t="inlineStr">
+        <is>
+          <t>Hi KING TECHNOLOGY,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR39" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -7910,7 +8177,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -7989,7 +8256,11 @@
           <t>918147148767</t>
         </is>
       </c>
-      <c r="S40" s="2" t="inlineStr"/>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/918147148767?text=Hi%20MY%20DISTRIBUTOR%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
           <t>6281040558</t>
@@ -8083,9 +8354,29 @@
         </is>
       </c>
       <c r="AN40" s="2" t="inlineStr"/>
-      <c r="AO40" s="2" t="inlineStr"/>
-      <c r="AP40" s="2" t="inlineStr"/>
-      <c r="AQ40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr">
+        <is>
+          <t>Hi MY DISTRIBUTOR,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP40" s="2" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for MY DISTRIBUTOR</t>
+        </is>
+      </c>
+      <c r="AQ40" s="2" t="inlineStr">
+        <is>
+          <t>Hi MY DISTRIBUTOR,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR40" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:55</t>
@@ -8100,7 +8391,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -8179,7 +8470,11 @@
           <t>919513533180</t>
         </is>
       </c>
-      <c r="S41" s="4" t="inlineStr"/>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/919513533180?text=Hi%20CAMERA%20COUNTRY%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T41" s="4" t="inlineStr">
         <is>
           <t>+91-9513533180; +919513533180; 9513533180</t>
@@ -8273,9 +8568,29 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="AO41" s="4" t="inlineStr"/>
-      <c r="AP41" s="4" t="inlineStr"/>
-      <c r="AQ41" s="4" t="inlineStr"/>
+      <c r="AO41" s="4" t="inlineStr">
+        <is>
+          <t>Hi CAMERA COUNTRY,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP41" s="4" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for CAMERA COUNTRY</t>
+        </is>
+      </c>
+      <c r="AQ41" s="4" t="inlineStr">
+        <is>
+          <t>Hi CAMERA COUNTRY,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR41" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:57</t>
@@ -8290,7 +8605,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -8369,7 +8684,11 @@
           <t>917353033399</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr"/>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/917353033399?text=Hi%20Star%20vision%20solutions%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
           <t>+91 7353033399; +91 7892988076; 7353033399</t>
@@ -8455,9 +8774,29 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="AO42" s="2" t="inlineStr"/>
-      <c r="AP42" s="2" t="inlineStr"/>
-      <c r="AQ42" s="2" t="inlineStr"/>
+      <c r="AO42" s="2" t="inlineStr">
+        <is>
+          <t>Hi Star vision solutions,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP42" s="2" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for Star vision solutions</t>
+        </is>
+      </c>
+      <c r="AQ42" s="2" t="inlineStr">
+        <is>
+          <t>Hi Star vision solutions,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR42" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -8472,7 +8811,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -8621,9 +8960,29 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="AO43" s="4" t="inlineStr"/>
-      <c r="AP43" s="4" t="inlineStr"/>
-      <c r="AQ43" s="4" t="inlineStr"/>
+      <c r="AO43" s="4" t="inlineStr">
+        <is>
+          <t>Hi VISION ZOOM SECURITY SYSTEMS,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP43" s="4" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for VISION ZOOM SECURITY SYSTEMS</t>
+        </is>
+      </c>
+      <c r="AQ43" s="4" t="inlineStr">
+        <is>
+          <t>Hi VISION ZOOM SECURITY SYSTEMS,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR43" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:55</t>
@@ -8638,7 +8997,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -8717,7 +9076,11 @@
           <t>919686037552</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/919686037552?text=Hi%20HM%20Security%20Solutions%20%28CCTV%20Sales%20%26%20Service%29%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
           <t>6616527297; 6771901355; 9686037552</t>
@@ -8799,9 +9162,29 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="AO44" s="2" t="inlineStr"/>
-      <c r="AP44" s="2" t="inlineStr"/>
-      <c r="AQ44" s="2" t="inlineStr"/>
+      <c r="AO44" s="2" t="inlineStr">
+        <is>
+          <t>Hi HM Security Solutions (CCTV Sales &amp; Service),
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP44" s="2" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for HM Security Solutions (CCTV Sales &amp; Service)</t>
+        </is>
+      </c>
+      <c r="AQ44" s="2" t="inlineStr">
+        <is>
+          <t>Hi HM Security Solutions (CCTV Sales &amp; Service),
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR44" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -8816,7 +9199,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -8895,7 +9278,11 @@
           <t>918618084202</t>
         </is>
       </c>
-      <c r="S45" s="4" t="inlineStr"/>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/918618084202?text=Hi%20Bangalore%20It%20Hub%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T45" s="4" t="inlineStr">
         <is>
           <t>+91 8618084202; +918618084202; 6215384432</t>
@@ -8977,9 +9364,29 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="AO45" s="4" t="inlineStr"/>
-      <c r="AP45" s="4" t="inlineStr"/>
-      <c r="AQ45" s="4" t="inlineStr"/>
+      <c r="AO45" s="4" t="inlineStr">
+        <is>
+          <t>Hi Bangalore It Hub,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP45" s="4" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for Bangalore It Hub</t>
+        </is>
+      </c>
+      <c r="AQ45" s="4" t="inlineStr">
+        <is>
+          <t>Hi Bangalore It Hub,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR45" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:55</t>
@@ -8994,7 +9401,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -9073,7 +9480,11 @@
           <t>918618682725</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/918618682725?text=Hi%20Mayur%20Infotech%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
           <t>+918618682725; 8011444930; 8618682725</t>
@@ -9155,9 +9566,29 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="AO46" s="2" t="inlineStr"/>
-      <c r="AP46" s="2" t="inlineStr"/>
-      <c r="AQ46" s="2" t="inlineStr"/>
+      <c r="AO46" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mayur Infotech,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP46" s="2" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for Mayur Infotech</t>
+        </is>
+      </c>
+      <c r="AQ46" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mayur Infotech,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR46" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:56</t>
@@ -9172,7 +9603,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -9251,7 +9682,11 @@
           <t>919916161100</t>
         </is>
       </c>
-      <c r="S47" s="4" t="inlineStr"/>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/919916161100?text=Hi%20Rajlaxmi%20infotech%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T47" s="4" t="inlineStr">
         <is>
           <t>+91 9916161100; +919916161100</t>
@@ -9333,9 +9768,29 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="AO47" s="4" t="inlineStr"/>
-      <c r="AP47" s="4" t="inlineStr"/>
-      <c r="AQ47" s="4" t="inlineStr"/>
+      <c r="AO47" s="4" t="inlineStr">
+        <is>
+          <t>Hi Rajlaxmi infotech,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP47" s="4" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for Rajlaxmi infotech</t>
+        </is>
+      </c>
+      <c r="AQ47" s="4" t="inlineStr">
+        <is>
+          <t>Hi Rajlaxmi infotech,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR47" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:57</t>
@@ -9343,10 +9798,14 @@
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="2" t="inlineStr"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>cid_16943958218051604871</t>
+        </is>
+      </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -9371,7 +9830,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Zirakpur</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -9425,7 +9884,11 @@
           <t>916239110669</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr"/>
+      <c r="S48" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/916239110669?text=Hi%20Web%20Plus%20Security%20System%2C%0ASaw%20your%20CCTV%20website%20in%20Zirakpur.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
           <t>+91 9115704767; 9115704767; 9467284332</t>
@@ -9507,9 +9970,29 @@
         </is>
       </c>
       <c r="AN48" s="2" t="inlineStr"/>
-      <c r="AO48" s="2" t="inlineStr"/>
-      <c r="AP48" s="2" t="inlineStr"/>
-      <c r="AQ48" s="2" t="inlineStr"/>
+      <c r="AO48" s="2" t="inlineStr">
+        <is>
+          <t>Hi Web Plus Security System,
+Saw your CCTV website in Zirakpur. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP48" s="2" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for Web Plus Security System</t>
+        </is>
+      </c>
+      <c r="AQ48" s="2" t="inlineStr">
+        <is>
+          <t>Hi Web Plus Security System,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR48" s="2" t="inlineStr">
         <is>
           <t>2026-10-08 16:39:53</t>
@@ -9524,7 +10007,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -9603,7 +10086,11 @@
           <t>919035362143</t>
         </is>
       </c>
-      <c r="S49" s="4" t="inlineStr"/>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/919035362143?text=Hi%20Yendra%20Techno%20Solution%20-%20CCTV%20Cameras%20Installation%20in%20Bengaluru%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T49" s="4" t="inlineStr">
         <is>
           <t>+919035362143; +919353316120</t>
@@ -9685,9 +10172,29 @@
         </is>
       </c>
       <c r="AN49" s="4" t="inlineStr"/>
-      <c r="AO49" s="4" t="inlineStr"/>
-      <c r="AP49" s="4" t="inlineStr"/>
-      <c r="AQ49" s="4" t="inlineStr"/>
+      <c r="AO49" s="4" t="inlineStr">
+        <is>
+          <t>Hi Yendra Techno Solution - CCTV Cameras Installation in Bengaluru,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP49" s="4" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for Yendra Techno Solution - CCTV Cameras Installation in Bengaluru</t>
+        </is>
+      </c>
+      <c r="AQ49" s="4" t="inlineStr">
+        <is>
+          <t>Hi Yendra Techno Solution - CCTV Cameras Installation in Bengaluru,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR49" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -9702,7 +10209,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -9781,7 +10288,11 @@
           <t>916361264243</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr"/>
+      <c r="S50" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/916361264243?text=Hi%20CCTV%20Surveillance%20Cameras%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
           <t>+916361264243; 6060429773; 6361264243</t>
@@ -9871,9 +10382,29 @@
         </is>
       </c>
       <c r="AN50" s="2" t="inlineStr"/>
-      <c r="AO50" s="2" t="inlineStr"/>
-      <c r="AP50" s="2" t="inlineStr"/>
-      <c r="AQ50" s="2" t="inlineStr"/>
+      <c r="AO50" s="2" t="inlineStr">
+        <is>
+          <t>Hi CCTV Surveillance Cameras,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP50" s="2" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for CCTV Surveillance Cameras</t>
+        </is>
+      </c>
+      <c r="AQ50" s="2" t="inlineStr">
+        <is>
+          <t>Hi CCTV Surveillance Cameras,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR50" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -9888,7 +10419,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -10045,9 +10576,29 @@
         </is>
       </c>
       <c r="AN51" s="4" t="inlineStr"/>
-      <c r="AO51" s="4" t="inlineStr"/>
-      <c r="AP51" s="4" t="inlineStr"/>
-      <c r="AQ51" s="4" t="inlineStr"/>
+      <c r="AO51" s="4" t="inlineStr">
+        <is>
+          <t>Hi MY COMPUTER AND CCTV ZONE,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP51" s="4" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for MY COMPUTER AND CCTV ZONE</t>
+        </is>
+      </c>
+      <c r="AQ51" s="4" t="inlineStr">
+        <is>
+          <t>Hi MY COMPUTER AND CCTV ZONE,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR51" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -10062,7 +10613,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -10141,7 +10692,11 @@
           <t>917026113516</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr"/>
+      <c r="S52" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/917026113516?text=Hi%20i2secure%20%E2%80%93%20Smart%20CCTV%20Solutions%20Bengaluru%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
           <t>+917026113516; 7026113516</t>
@@ -10219,9 +10774,29 @@
         </is>
       </c>
       <c r="AN52" s="2" t="inlineStr"/>
-      <c r="AO52" s="2" t="inlineStr"/>
-      <c r="AP52" s="2" t="inlineStr"/>
-      <c r="AQ52" s="2" t="inlineStr"/>
+      <c r="AO52" s="2" t="inlineStr">
+        <is>
+          <t>Hi i2secure – Smart CCTV Solutions Bengaluru,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP52" s="2" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for i2secure – Smart CCTV Solutions Bengaluru</t>
+        </is>
+      </c>
+      <c r="AQ52" s="2" t="inlineStr">
+        <is>
+          <t>Hi i2secure – Smart CCTV Solutions Bengaluru,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR52" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -10236,7 +10811,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -10315,7 +10890,11 @@
           <t>918660317664</t>
         </is>
       </c>
-      <c r="S53" s="4" t="inlineStr"/>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/918660317664?text=Hi%20Agasthya%20Electronics%20%7C%20CCTV%2C%20Solar%20Sim%20Cameras%2C%20Wi-Fi%20Cameras%2C%20Digital%20Door%20Locks%2C%20Video%20Door%20Phones%2C%20Access%20Control%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T53" s="4" t="inlineStr">
         <is>
           <t>8660317664; 9096313912</t>
@@ -10417,9 +10996,29 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="AO53" s="4" t="inlineStr"/>
-      <c r="AP53" s="4" t="inlineStr"/>
-      <c r="AQ53" s="4" t="inlineStr"/>
+      <c r="AO53" s="4" t="inlineStr">
+        <is>
+          <t>Hi Agasthya Electronics | CCTV, Solar Sim Cameras, Wi-Fi Cameras, Digital Door Locks, Video Door Phones, Access Control,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP53" s="4" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for Agasthya Electronics | CCTV, Solar Sim Cameras, Wi-Fi Cameras, Digital Door Locks, Video Door Phones, Access Control</t>
+        </is>
+      </c>
+      <c r="AQ53" s="4" t="inlineStr">
+        <is>
+          <t>Hi Agasthya Electronics | CCTV, Solar Sim Cameras, Wi-Fi Cameras, Digital Door Locks, Video Door Phones, Access Control,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR53" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:56</t>
@@ -10434,7 +11033,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -10513,7 +11112,11 @@
           <t>919902234508</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr"/>
+      <c r="S54" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/919902234508?text=Hi%20CCTV%20ZONE%20IN%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
           <t>+919902234508; 9902234508</t>
@@ -10591,9 +11194,29 @@
         </is>
       </c>
       <c r="AN54" s="2" t="inlineStr"/>
-      <c r="AO54" s="2" t="inlineStr"/>
-      <c r="AP54" s="2" t="inlineStr"/>
-      <c r="AQ54" s="2" t="inlineStr"/>
+      <c r="AO54" s="2" t="inlineStr">
+        <is>
+          <t>Hi CCTV ZONE IN,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP54" s="2" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for CCTV ZONE IN</t>
+        </is>
+      </c>
+      <c r="AQ54" s="2" t="inlineStr">
+        <is>
+          <t>Hi CCTV ZONE IN,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR54" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -10608,7 +11231,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -10687,7 +11310,11 @@
           <t>919980040399</t>
         </is>
       </c>
-      <c r="S55" s="4" t="inlineStr"/>
+      <c r="S55" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/919980040399?text=Hi%20MYF%20CCTV%20%26%20security%20systems%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T55" s="4" t="inlineStr">
         <is>
           <t>+91 9980040399; +919980040399; 9980040399</t>
@@ -10769,9 +11396,29 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="AO55" s="4" t="inlineStr"/>
-      <c r="AP55" s="4" t="inlineStr"/>
-      <c r="AQ55" s="4" t="inlineStr"/>
+      <c r="AO55" s="4" t="inlineStr">
+        <is>
+          <t>Hi MYF CCTV &amp; security systems,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP55" s="4" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for MYF CCTV &amp; security systems</t>
+        </is>
+      </c>
+      <c r="AQ55" s="4" t="inlineStr">
+        <is>
+          <t>Hi MYF CCTV &amp; security systems,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR55" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -10786,7 +11433,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -10865,7 +11512,11 @@
           <t>919739661248</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr"/>
+      <c r="S56" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/919739661248?text=Hi%20Computer%20IT%20Mart%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
           <t>+91 9620554635; +91 9739661248; 6267352236</t>
@@ -10959,9 +11610,29 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="AO56" s="2" t="inlineStr"/>
-      <c r="AP56" s="2" t="inlineStr"/>
-      <c r="AQ56" s="2" t="inlineStr"/>
+      <c r="AO56" s="2" t="inlineStr">
+        <is>
+          <t>Hi Computer IT Mart,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP56" s="2" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for Computer IT Mart</t>
+        </is>
+      </c>
+      <c r="AQ56" s="2" t="inlineStr">
+        <is>
+          <t>Hi Computer IT Mart,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR56" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:56</t>
@@ -10976,7 +11647,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -11055,7 +11726,11 @@
           <t>917676954748</t>
         </is>
       </c>
-      <c r="S57" s="4" t="inlineStr"/>
+      <c r="S57" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/917676954748?text=Hi%20Anvi%20Tech%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T57" s="4" t="inlineStr"/>
       <c r="U57" s="4" t="inlineStr">
         <is>
@@ -11129,9 +11804,29 @@
         </is>
       </c>
       <c r="AN57" s="4" t="inlineStr"/>
-      <c r="AO57" s="4" t="inlineStr"/>
-      <c r="AP57" s="4" t="inlineStr"/>
-      <c r="AQ57" s="4" t="inlineStr"/>
+      <c r="AO57" s="4" t="inlineStr">
+        <is>
+          <t>Hi Anvi Tech,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP57" s="4" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for Anvi Tech</t>
+        </is>
+      </c>
+      <c r="AQ57" s="4" t="inlineStr">
+        <is>
+          <t>Hi Anvi Tech,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR57" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -11146,7 +11841,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -11225,7 +11920,11 @@
           <t>919353356153</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr"/>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/919353356153?text=Hi%20V-Tech%20-%20cctv%20cameras%20and%20installation%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
           <t>+919353356153; 7899999999</t>
@@ -11303,9 +12002,29 @@
         </is>
       </c>
       <c r="AN58" s="2" t="inlineStr"/>
-      <c r="AO58" s="2" t="inlineStr"/>
-      <c r="AP58" s="2" t="inlineStr"/>
-      <c r="AQ58" s="2" t="inlineStr"/>
+      <c r="AO58" s="2" t="inlineStr">
+        <is>
+          <t>Hi V-Tech - cctv cameras and installation,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP58" s="2" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for V-Tech - cctv cameras and installation</t>
+        </is>
+      </c>
+      <c r="AQ58" s="2" t="inlineStr">
+        <is>
+          <t>Hi V-Tech - cctv cameras and installation,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR58" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:55</t>
@@ -11320,7 +12039,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>PITCH_DRAFTED</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -11399,7 +12118,11 @@
           <t>919206979799</t>
         </is>
       </c>
-      <c r="S59" s="4" t="inlineStr"/>
+      <c r="S59" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/919206979799?text=Hi%20CCTV%20Shield%20Care%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+        </is>
+      </c>
       <c r="T59" s="4" t="inlineStr">
         <is>
           <t>+919449776044; 6564498876; 9449776044</t>
@@ -11481,9 +12204,29 @@
         </is>
       </c>
       <c r="AN59" s="4" t="inlineStr"/>
-      <c r="AO59" s="4" t="inlineStr"/>
-      <c r="AP59" s="4" t="inlineStr"/>
-      <c r="AQ59" s="4" t="inlineStr"/>
+      <c r="AO59" s="4" t="inlineStr">
+        <is>
+          <t>Hi CCTV Shield Care,
+Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
+We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
+Worth a quick look?</t>
+        </is>
+      </c>
+      <c r="AP59" s="4" t="inlineStr">
+        <is>
+          <t>AMC tracking &amp; technician panel for CCTV Shield Care</t>
+        </is>
+      </c>
+      <c r="AQ59" s="4" t="inlineStr">
+        <is>
+          <t>Hi CCTV Shield Care,
+I came across your website and wanted to reach out.
+Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
+We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
       <c r="AR59" s="4" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -11566,95 +12309,121 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V30" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA30" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V31" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V32" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V33" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X33" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y33" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA33" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB33" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V34" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V35" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V36" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V37" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X37" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y37" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z37" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB37" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V38" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V39" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X39" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V40" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X40" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y40" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA40" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB40" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V41" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X41" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y41" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V42" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V43" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V44" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V45" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V46" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V47" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V48" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X48" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V49" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA49" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V50" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y50" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA50" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB50" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V51" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X51" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y51" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V52" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V53" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X53" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y53" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z53" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA53" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB53" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V54" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V55" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V56" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X56" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y56" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA56" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V57" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V58" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V59" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X59" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y59" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S31" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V31" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S32" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V32" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V33" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X33" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y33" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA33" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB33" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S34" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V34" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V35" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V36" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V37" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X37" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y37" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z37" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB37" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V38" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V39" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X39" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V40" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X40" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y40" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA40" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB40" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V41" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X41" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y41" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V42" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V43" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V44" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V45" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V46" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V47" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V48" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X48" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V49" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA49" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S50" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V50" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y50" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA50" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB50" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V51" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X51" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y51" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S52" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V52" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S53" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V53" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X53" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y53" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z53" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA53" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB53" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S54" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V54" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V55" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V56" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X56" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y56" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AA56" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V57" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S58" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V58" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S59" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V59" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="X59" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y59" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -830,7 +830,7 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/917892328427?text=Hi%20SKYWAY%20INFOSYSTEMS%2C%0ANoticed%20your%20CCTV%20business%20in%2050%20gets%20great%20reviews%2C%20but%20you%20don%27t%20have%20a%20direct%20website%20yet%21%0A%0AYou%20might%20be%20losing%20direct%20Google%20customers%20or%20paying%20high%20commissions%20on%20Justdial.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F</t>
+          <t>https://wa.me/917892328427?text=Hi%20SKYWAY%20INFOSYSTEMS%2C%0ANoticed%20your%20security%20systems%20store%20in%20Bengaluru%20has%20strong%20footfall%2C%20but%20no%20dedicated%20web%20portal%20for%20wholesale%20and%20installer%20inquiries%21%0A%0AWe%20set%20up%20branded%20digital%20product%20catalogs%20with%20direct%20WhatsApp%20quote%20buttons%3A%0A%F0%9F%91%89%20Customer%20Website%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Warranty%20%26%20Technician%20Dispatch%20Admin%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AWorth%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr"/>
@@ -901,22 +901,404 @@
       <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>Hi SKYWAY INFOSYSTEMS,
-Noticed your CCTV business in 50 gets great reviews, but you don't have a direct website yet!
-You might be losing direct Google customers or paying high commissions on Justdial. We build complete turnkey setups for CCTV companies:
+Noticed your security systems store in Bengaluru has strong footfall, but no dedicated web portal for wholesale and installer inquiries!
+We set up branded digital product catalogs with direct WhatsApp quote buttons:
+👉 Customer Website: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Worth a quick 10-min walkthrough? - Atrya Solutions</t>
+        </is>
+      </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>Online Dealer Catalog &amp; Dispatch Panel for SKYWAY INFOSYSTEMS</t>
+        </is>
+      </c>
+      <c r="AQ2" s="2" t="inlineStr">
+        <is>
+          <t>Hi SKYWAY INFOSYSTEMS Management,
+I came across your security systems store in Bengaluru. While you have great local reputation, potential buyers searching Google for CCTV wholesale pricing and package installation cannot find an official portal.
+We build complete digital setups for security dealers:
+👉 Interactive Website with 1-click WhatsApp Quotes: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Could we connect for a brief 10-minute walkthrough this week?
+Best regards,
+Atrya Solutions Team
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 16:39:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ChIJUebeb0sRrjsRMSGR17c1mf8</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>PITCH_DRAFTED</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Mahadev Enterprises - Cctv installation, Camera installation, Camera Repair, camera for home installation, Video surveillance</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>CCTV &amp; Security Systems Dealer</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Devanna Building, 123/1, behind ITPL Main Road, Pattandur Agrahara, Whitefield, Bengaluru, Karnataka 560066, India</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>560066</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>12.982405199999999</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>77.73367929999999</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>https://maps.google.com/?cid=18417811214820254001&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONAL</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>096201 41315</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>919620141315</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>https://wa.me/919620141315?text=Hi%20Mahadev%20Enterprises%2C%0ANoticed%20your%20security%20systems%20store%20in%20Bengaluru%20has%20strong%20footfall%2C%20but%20no%20dedicated%20web%20portal%20for%20wholesale%20and%20installer%20inquiries%21%0A%0AWe%20set%20up%20branded%20digital%20product%20catalogs%20with%20direct%20WhatsApp%20quote%20buttons%3A%0A%F0%9F%91%89%20Customer%20Website%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Warranty%20%26%20Technician%20Dispatch%20Admin%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AWorth%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr"/>
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr"/>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="4" t="inlineStr"/>
+      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>no_website</t>
+        </is>
+      </c>
+      <c r="AF3" s="4" t="inlineStr">
+        <is>
+          <t>no_website</t>
+        </is>
+      </c>
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t>No official website (relies only on directories or social media)</t>
+        </is>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM3" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AN3" s="4" t="inlineStr"/>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>Hi Mahadev Enterprises,
+Noticed your security systems store in Bengaluru has strong footfall, but no dedicated web portal for wholesale and installer inquiries!
+We set up branded digital product catalogs with direct WhatsApp quote buttons:
+👉 Customer Website: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Worth a quick 10-min walkthrough? - Atrya Solutions</t>
+        </is>
+      </c>
+      <c r="AP3" s="4" t="inlineStr">
+        <is>
+          <t>Online Dealer Catalog &amp; Dispatch Panel for Mahadev Enterprises</t>
+        </is>
+      </c>
+      <c r="AQ3" s="4" t="inlineStr">
+        <is>
+          <t>Hi Mahadev Enterprises Management,
+I came across your security systems store in Bengaluru. While you have great local reputation, potential buyers searching Google for CCTV wholesale pricing and package installation cannot find an official portal.
+We build complete digital setups for security dealers:
+👉 Interactive Website with 1-click WhatsApp Quotes: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Could we connect for a brief 10-minute walkthrough this week?
+Best regards,
+Atrya Solutions Team
+Reply STOP and I won't contact you again.</t>
+        </is>
+      </c>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10 09:50:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ChIJzaqqqvM9rjsRiFywQEyOKF0</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>PITCH_DRAFTED</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Indo Spy</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>CCTV &amp; Security Systems Dealer</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>104, 1st Floor, Bengaluru Business Centre, Osman Khan Road, NR Rd, near NR Road, beside Axis Bank, Kumbaragundi, Kalasipalya, Bengaluru, Karnataka 560002, India</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>560002</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>12.962954</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>77.58377229999999</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>https://maps.google.com/?cid=6712771702749682824&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONAL</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>095916 32888</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>919591632888</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>https://wa.me/919591632888?text=Hi%20Indo%20Spy%2C%0ANoticed%20your%20CCTV%20installation%20business%20in%20Bengaluru%20gets%20great%20reviews%2C%20but%20potential%20customers%20searching%20Google%20can%27t%20find%20a%20direct%20website%20for%20quote%20inquiries%21%0A%0ARelying%20only%20on%20directories%20means%20paying%20high%20commissions%20and%20sharing%20leads%20with%20competitors.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F%20-%20Atrya%20Solutions</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>no_website</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>no_website</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>No official website (relies only on directories or social media)</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM4" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AN4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>Hi Indo Spy,
+Noticed your CCTV installation business in Bengaluru gets great reviews, but potential customers searching Google can't find a direct website for quote inquiries!
+Relying only on directories means paying high commissions and sharing leads with competitors. We build complete turnkey setups for CCTV companies:
 👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
 👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
-Open for a quick 10-min walkthrough this week?</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr">
-        <is>
-          <t>Direct Customer Website &amp; AMC Admin Panel for SKYWAY INFOSYSTEMS</t>
-        </is>
-      </c>
-      <c r="AQ2" s="2" t="inlineStr">
-        <is>
-          <t>Hi SKYWAY INFOSYSTEMS Team,
-I came across your CCTV business in 50 and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Open for a quick 10-min walkthrough this week? - Atrya Solutions</t>
+        </is>
+      </c>
+      <c r="AP4" s="2" t="inlineStr">
+        <is>
+          <t>Direct Customer Website &amp; AMC Admin Panel for Indo Spy</t>
+        </is>
+      </c>
+      <c r="AQ4" s="2" t="inlineStr">
+        <is>
+          <t>Hi Indo Spy Team,
+I came across your CCTV business in Bengaluru and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
 Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
 At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
 1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
@@ -930,383 +1312,6 @@
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
-      <c r="AR2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08 16:39:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>ChIJUebeb0sRrjsRMSGR17c1mf8</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>PITCH_DRAFTED</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Mahadev Enterprises - Cctv installation, Camera installation, Camera Repair, camera for home installation, Video surveillance</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>CCTV &amp; Security Systems Dealer</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Devanna Building, 123/1, behind ITPL Main Road, Pattandur Agrahara, Whitefield, Bengaluru, Karnataka 560066, India</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>560066</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>12.982405199999999</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>77.73367929999999</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>https://maps.google.com/?cid=18417811214820254001&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONAL</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>096201 41315</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>919620141315</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>https://wa.me/919620141315?text=Hi%20from%20Atrya%20Solutions%21%20%0A%0AAre%20you%20losing%20direct%20Google%20customers%20to%20competitors%20and%20paying%20heavy%20commissions%20to%20Justdial/IndiaMart%3F%0A%0AWe%20build%20turnkey%20digital%20systems%20for%20CCTV%20companies.%20Get%20a%20high-converting%20customer%20website%20with%201-click%20WhatsApp%20quotes%20AND%20an%20admin%20panel%20for%20technician%20dispatch/AMC%20management.%0A%0ASee%20LIVE%20DEMO%3A%20https%3A//atryasolutions.netlify.app/%20%0A%0ALet%27s%20chat%20for%2010%20mins%3F</t>
-        </is>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="inlineStr"/>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr"/>
-      <c r="Z3" s="4" t="inlineStr"/>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr">
-        <is>
-          <t>no_website</t>
-        </is>
-      </c>
-      <c r="AF3" s="4" t="inlineStr">
-        <is>
-          <t>no_website</t>
-        </is>
-      </c>
-      <c r="AG3" s="4" t="inlineStr">
-        <is>
-          <t>No official website (relies only on directories or social media)</t>
-        </is>
-      </c>
-      <c r="AH3" s="4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AJ3" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AL3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM3" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr">
-        <is>
-          <t>Hi from Atrya Solutions! 
-Are you losing direct Google customers to competitors and paying heavy commissions to Justdial/IndiaMart?
-We build turnkey digital systems for CCTV companies. Get a high-converting customer website with 1-click WhatsApp quotes AND an admin panel for technician dispatch/AMC management.
-See LIVE DEMO: https://atryasolutions.netlify.app/ 
-Let's chat for 10 mins?</t>
-        </is>
-      </c>
-      <c r="AP3" s="4" t="inlineStr">
-        <is>
-          <t>Stop Losing Direct CCTV Customers</t>
-        </is>
-      </c>
-      <c r="AQ3" s="4" t="inlineStr">
-        <is>
-          <t>Dear Mahadev Enterprises,
-Are you tired of losing direct Google customers to competitors and paying hefty commissions to directories?
-Atrya Solutions builds turnkey digital systems for CCTV companies like yours. Get a high-converting customer website with instant WhatsApp quote buttons (LIVE DEMO: https://atryasolutions.netlify.app/) AND an operations/AMC dispatch admin panel (LIVE DEMO: https://atryasolutions.netlify.app/admin).
-This combo gives you direct high-value customer inquiries and automates your technician &amp; AMC management.
-Would you be open to a quick 10-15 minute walkthrough?
-Reply STOP and I won't contact you again.</t>
-        </is>
-      </c>
-      <c r="AR3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-10 09:50:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>ChIJzaqqqvM9rjsRiFywQEyOKF0</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>PITCH_DRAFTED</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Indo Spy</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>CCTV &amp; Security Systems Dealer</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>104, 1st Floor, Bengaluru Business Centre, Osman Khan Road, NR Rd, near NR Road, beside Axis Bank, Kumbaragundi, Kalasipalya, Bengaluru, Karnataka 560002, India</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>560002</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12.962954</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>77.58377229999999</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>https://maps.google.com/?cid=6712771702749682824&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONAL</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>095916 32888</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>919591632888</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>https://wa.me/919591632888?text=Hi%20Indo%20Spy%20team%2C%0A%0AI%20noticed%20you%20don%E2%80%99t%20have%20a%20dedicated%20website%2C%20so%20you%E2%80%99re%20likely%20missing%20direct%20Google%20leads%20and%20paying%20hefty%20directory%20fees.%0A%0AWe%20build%20a%20high%E2%80%91converting%20site%20with%201%E2%80%91click%20WhatsApp%20quote%20buttons%20%26%20lead%20forms%2C%20plus%20an%20admin%20panel%20for%20tech%20dispatch%20%26%20AMC%20alerts.%0A%0ACheck%20the%20LIVE%20DEMOs%3A%0ACustomer%20site%3A%20https%3A//atryasolutions.netlify.app/%0AAdmin%20panel%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0ACan%20we%20schedule%20a%2010%E2%80%9115%E2%80%AFmin%20walkthrough%3F</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr"/>
-      <c r="Z4" s="2" t="inlineStr"/>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>no_website</t>
-        </is>
-      </c>
-      <c r="AF4" s="2" t="inlineStr">
-        <is>
-          <t>no_website</t>
-        </is>
-      </c>
-      <c r="AG4" s="2" t="inlineStr">
-        <is>
-          <t>No official website (relies only on directories or social media)</t>
-        </is>
-      </c>
-      <c r="AH4" s="2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AI4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AJ4" s="2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AL4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM4" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr">
-        <is>
-          <t>Hi Indo Spy team,
-I noticed you don’t have a dedicated website, so you’re likely missing direct Google leads and paying hefty directory fees.
-We build a high‑converting site with 1‑click WhatsApp quote buttons &amp; lead forms, plus an admin panel for tech dispatch &amp; AMC alerts.
-Check the LIVE DEMOs:
-Customer site: https://atryasolutions.netlify.app/
-Admin panel: https://atryasolutions.netlify.app/admin
-Can we schedule a 10‑15 min walkthrough?</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="inlineStr">
-        <is>
-          <t>Boost Direct Leads &amp; Ops</t>
-        </is>
-      </c>
-      <c r="AQ4" s="2" t="inlineStr">
-        <is>
-          <t>Hi Indo Spy,
-I see you currently rely on directories for leads, which means you’re paying commissions and losing direct Google customers to competitors. Atrya Solutions can turn that around with a turnkey website that captures high‑value inquiries instantly via 1‑click WhatsApp quote buttons and online lead forms—no more middle‑man fees.
-Alongside, our Operations &amp; AMC Dispatch Admin panel automates technician scheduling, warranty tracking, and service renewal alerts, freeing your team to focus on installations.
-Take a look at the LIVE DEMOs we customize for CCTV firms:
-Customer site: https://atryasolutions.netlify.app/
-Admin panel: https://atryasolutions.netlify.app/admin
-Would you have 10‑15 minutes for a quick walkthrough? Reply STOP and I won't contact you again.</t>
-        </is>
-      </c>
       <c r="AR4" s="2" t="inlineStr">
         <is>
           <t>2026-10-10 09:50:54</t>
@@ -1402,7 +1407,7 @@
       </c>
       <c r="S5" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/918971812021?text=Hi%20from%20Atrya%20Solutions%21%20Your%204.9-star%20rating%20is%20impressive.%20Imagine%20capturing%20direct%20Google%20customers%20via%20WhatsApp%2C%20instead%20of%20Justdial/IndiaMart%20commissions.%20We%20build%20high-converting%20websites%20%2B%20automate%20your%20technician%20dispatch%20%26%20AMC%20schedules.%20Let%27s%20chat%20for%2010%20mins%3F</t>
+          <t>https://wa.me/918971812021?text=Hi%20CCTV%20STORE%20IN%2C%0ANoticed%20your%20security%20systems%20store%20in%20Bengaluru%20has%20strong%20footfall%2C%20but%20no%20dedicated%20web%20portal%20for%20wholesale%20and%20installer%20inquiries%21%0A%0AWe%20set%20up%20branded%20digital%20product%20catalogs%20with%20direct%20WhatsApp%20quote%20buttons%3A%0A%F0%9F%91%89%20Customer%20Website%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Warranty%20%26%20Technician%20Dispatch%20Admin%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AWorth%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr"/>
@@ -1472,22 +1477,29 @@
       <c r="AN5" s="4" t="inlineStr"/>
       <c r="AO5" s="4" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions! Your 4.9-star rating is impressive. Imagine capturing direct Google customers via WhatsApp, instead of Justdial/IndiaMart commissions. We build high-converting websites + automate your technician dispatch &amp; AMC schedules. Let's chat for 10 mins?</t>
+          <t>Hi CCTV STORE IN,
+Noticed your security systems store in Bengaluru has strong footfall, but no dedicated web portal for wholesale and installer inquiries!
+We set up branded digital product catalogs with direct WhatsApp quote buttons:
+👉 Customer Website: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Worth a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP5" s="4" t="inlineStr">
         <is>
-          <t>Boost Leads &amp; Automate Operations (CCTV STORE IN)</t>
+          <t>Online Dealer Catalog &amp; Dispatch Panel for CCTV STORE IN</t>
         </is>
       </c>
       <c r="AQ5" s="4" t="inlineStr">
         <is>
-          <t>Dear CCTV STORE IN Team,
-Your excellent reviews show strong customer trust. However, relying solely on directories means losing direct Google customers to competitors and paying hefty commissions.
-We offer a turnkey solution:
-1.  **High-Converting Customer Website** (LIVE DEMO: https://atryasolutions.netlify.app/)
-2.  **Operations &amp; AMC Dispatch Admin** (LIVE DEMO: https://atryasolutions.netlify.app/admin)
-This combo captures direct WhatsApp inquiries and automates technician management, boosting your ROI. Would you be open to a quick 10-15 minute walkthrough?
+          <t>Hi CCTV STORE IN Management,
+I came across your security systems store in Bengaluru. While you have great local reputation, potential buyers searching Google for CCTV wholesale pricing and package installation cannot find an official portal.
+We build complete digital setups for security dealers:
+👉 Interactive Website with 1-click WhatsApp Quotes: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Could we connect for a brief 10-minute walkthrough this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1586,7 +1598,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/918050452832?text=Hi%20%5BName%5D%2C%0AI%20noticed%20MY%20CHOICE%20IT%20HUB%20relies%20only%20on%20directories%2C%20missing%20direct%20Google%20leads%20and%20paying%20high%20commissions.%20Atrya%E2%80%99s%20LIVE%20DEMO%20shows%20a%20high%E2%80%91converting%20website%20with%201%E2%80%91click%20WhatsApp%20quote%20buttons%20%2B%20an%20Operations%20%26%20AMC%20admin%20panel%20that%20automates%20dispatch%20and%20renewals.%0ACan%20we%20schedule%20a%2010%E2%80%9115%E2%80%AFmin%20walkthrough%3F%0AReply%20STOP%20and%20I%20won%27t%20contact%20you%20again.</t>
+          <t>https://wa.me/918050452832?text=Hi%20MY%20CHOICE%20IT%20HUB%20team%2C%0ASaw%20your%20IT%20%26%20networking%20hub%20in%20Bengaluru.%20Most%20IT%20dealers%20handle%20CCTV%20and%20AMC%20inquiries%2C%20but%20lose%20high-margin%20corporate%20clients%20because%20they%20don%27t%20have%20a%20direct%20quote%20catalog%20online.%0A%0AWe%20build%20turnkey%20systems%20for%20IT%20%26%20CCTV%20hardware%20providers%3A%0A%F0%9F%91%89%201-Click%20WhatsApp%20Quote%20Website%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20AMC%20Maintenance%20%26%20Technician%20Dispatch%20Admin%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20demo%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr"/>
@@ -1656,23 +1668,29 @@
       <c r="AN6" s="2" t="inlineStr"/>
       <c r="AO6" s="2" t="inlineStr">
         <is>
-          <t>Hi [Name],
-I noticed MY CHOICE IT HUB relies only on directories, missing direct Google leads and paying high commissions. Atrya’s LIVE DEMO shows a high‑converting website with 1‑click WhatsApp quote buttons + an Operations &amp; AMC admin panel that automates dispatch and renewals.
-Can we schedule a 10‑15 min walkthrough?
-Reply STOP and I won't contact you again.</t>
+          <t>Hi MY CHOICE IT HUB team,
+Saw your IT &amp; networking hub in Bengaluru. Most IT dealers handle CCTV and AMC inquiries, but lose high-margin corporate clients because they don't have a direct quote catalog online.
+We build turnkey systems for IT &amp; CCTV hardware providers:
+👉 1-Click WhatsApp Quote Website: https://atryasolutions.netlify.app/
+👉 AMC Maintenance &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min demo? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP6" s="2" t="inlineStr">
         <is>
-          <t>Capture Direct Google Leads</t>
+          <t>Direct Corporate Leads &amp; AMC Panel for MY CHOICE IT HUB</t>
         </is>
       </c>
       <c r="AQ6" s="2" t="inlineStr">
         <is>
-          <t>Hi [Name],
-I’ve observed that MY CHOICE IT HUB currently depends on directory listings, which means you’re losing direct Google customers and paying hefty commissions to platforms like Justdial and IndiaMart.
-Atrya Solutions builds a turnkey digital system for CCTV firms. Our LIVE DEMO (https://atryasolutions.netlify.app/) showcases a high‑converting website with instant 1‑click WhatsApp quote buttons and online lead forms, turning Google searches into qualified inquiries. The companion Operations &amp; AMC Dispatch Admin (https://atryasolutions.netlify.app/admin) automates technician scheduling, warranty tracking, and service renewal alerts—saving time and boosting ROI.
-Would you have 10‑15 minutes for a quick walkthrough?
+          <t>Hi MY CHOICE IT HUB Team,
+I came across your hardware &amp; networking hub in Bengaluru. Many IT firms handle CCTV and networking installations but lose high-margin corporate clients because they lack a dedicated website showcasing their solutions.
+We build turnkey systems for IT &amp; CCTV hardware providers:
+1. Instant WhatsApp Quote &amp; Product Catalog: https://atryasolutions.netlify.app/
+2. AMC Maintenance &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute demo to see how this brings direct inquiries without directory commissions?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1771,7 +1789,7 @@
       </c>
       <c r="S7" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919113207306?text=Hi%20AMBE%20Security%2C%0A%0AI%20noticed%20you%20don%E2%80%99t%20have%20a%20dedicated%20website%2C%20so%20you%E2%80%99re%20likely%20missing%20direct%20Google%20leads%20and%20paying%20heavy%20commissions%20to%20directories.%0A%0AWe%20launch%20a%20live%2C%20high%E2%80%91converting%20site%20with%201%E2%80%91click%20WhatsApp%20quote%20buttons%20%2B%20an%20admin%20panel%20that%20dispatches%20technicians%20%26%20manages%20AMCs.%0A%0ASee%20the%20LIVE%20DEMOs%3A%0ACustomer%20site%3A%20https%3A//atryasolutions.netlify.app/%0AAdmin%20panel%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0ACan%20we%20schedule%20a%2010%E2%80%9115%E2%80%AFmin%20walkthrough%3F</t>
+          <t>https://wa.me/919113207306?text=Hi%20AMBE%20SECURITY%20SYSTEMS%2C%0ANoticed%20your%20security%20systems%20store%20in%20Bengaluru%20has%20strong%20footfall%2C%20but%20no%20dedicated%20web%20portal%20for%20wholesale%20and%20installer%20inquiries%21%0A%0AWe%20set%20up%20branded%20digital%20product%20catalogs%20with%20direct%20WhatsApp%20quote%20buttons%3A%0A%F0%9F%91%89%20Customer%20Website%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Warranty%20%26%20Technician%20Dispatch%20Admin%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AWorth%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr"/>
@@ -1841,29 +1859,29 @@
       <c r="AN7" s="4" t="inlineStr"/>
       <c r="AO7" s="4" t="inlineStr">
         <is>
-          <t>Hi AMBE Security,
-I noticed you don’t have a dedicated website, so you’re likely missing direct Google leads and paying heavy commissions to directories.
-We launch a live, high‑converting site with 1‑click WhatsApp quote buttons + an admin panel that dispatches technicians &amp; manages AMCs.
-See the LIVE DEMOs:
-Customer site: https://atryasolutions.netlify.app/
-Admin panel: https://atryasolutions.netlify.app/admin
-Can we schedule a 10‑15 min walkthrough?</t>
+          <t>Hi AMBE SECURITY SYSTEMS,
+Noticed your security systems store in Bengaluru has strong footfall, but no dedicated web portal for wholesale and installer inquiries!
+We set up branded digital product catalogs with direct WhatsApp quote buttons:
+👉 Customer Website: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Worth a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP7" s="4" t="inlineStr">
         <is>
-          <t>Capture Direct Leads, Cut Commissions</t>
+          <t>Online Dealer Catalog &amp; Dispatch Panel for AMBE SECURITY SYSTEMS</t>
         </is>
       </c>
       <c r="AQ7" s="4" t="inlineStr">
         <is>
-          <t>Hi [Name],
-I’ve observed that AMBE Security Systems currently relies on directories for leads. That means you’re paying steep commissions while missing out on direct Google customers who prefer instant contact.
-Atrya Solutions builds a turnkey, high‑converting website with a 1‑click WhatsApp quote button and an online lead form—so every Google search converts into a qualified inquiry. Paired with our Operations &amp; AMC Dispatch Admin panel, you can automate technician scheduling, warranty tracking, and service renewal alerts.
-You can explore the exact experience we deliver via these LIVE DEMOs:
-Customer site: https://atryasolutions.netlify.app/
-Admin panel: https://atryasolutions.netlify.app/admin
-Would you have 10‑15 minutes this week for a quick walkthrough?
+          <t>Hi AMBE SECURITY SYSTEMS Management,
+I came across your security systems store in Bengaluru. While you have great local reputation, potential buyers searching Google for CCTV wholesale pricing and package installation cannot find an official portal.
+We build complete digital setups for security dealers:
+👉 Interactive Website with 1-click WhatsApp Quotes: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Could we connect for a brief 10-minute walkthrough this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1962,7 +1980,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919013515533?text=Hi%20from%20Atrya%20Solutions%21%20%0A%0AAre%20you%20losing%20direct%20Google%20customers%20to%20competitors%20or%20paying%20hefty%20commissions%20to%20Justdial/IndiaMart%3F%0A%0AWe%20build%20turnkey%20digital%20systems%20for%20CCTV%20companies.%20Get%20a%20high-converting%20customer%20website%20with%20WhatsApp%20quotes%20%2B%20an%20admin%20panel%20for%20job%20dispatch%20%26%20AMC%20management.%0A%0ASee%20a%20LIVE%20DEMO%3A%20https%3A//atryasolutions.netlify.app/%20and%20https%3A//atryasolutions.netlify.app/admin%0A%0ALet%27s%20chat%20for%2010%20mins%3F</t>
+          <t>https://wa.me/919013515533?text=Hi%20SPY%20HUB%20CCTV%20SALES%20AND%20SERVICES%2C%0ANoticed%20your%20CCTV%20installation%20business%20in%20Bengaluru%20gets%20great%20reviews%2C%20but%20potential%20customers%20searching%20Google%20can%27t%20find%20a%20direct%20website%20for%20quote%20inquiries%21%0A%0ARelying%20only%20on%20directories%20means%20paying%20high%20commissions%20and%20sharing%20leads%20with%20competitors.%20We%20build%20complete%20turnkey%20setups%20for%20CCTV%20companies%3A%0A%F0%9F%91%89%20Customer%20Website%20%281-Click%20WhatsApp%20Quotes%29%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Operations%20Admin%20%28Technician%20%26%20AMC%20Dispatch%29%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%20this%20week%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr"/>
@@ -2032,25 +2050,33 @@
       <c r="AN8" s="2" t="inlineStr"/>
       <c r="AO8" s="2" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions! 
-Are you losing direct Google customers to competitors or paying hefty commissions to Justdial/IndiaMart?
-We build turnkey digital systems for CCTV companies. Get a high-converting customer website with WhatsApp quotes + an admin panel for job dispatch &amp; AMC management.
-See a LIVE DEMO: https://atryasolutions.netlify.app/ and https://atryasolutions.netlify.app/admin
-Let's chat for 10 mins?</t>
+          <t>Hi SPY HUB CCTV SALES AND SERVICES,
+Noticed your CCTV installation business in Bengaluru gets great reviews, but potential customers searching Google can't find a direct website for quote inquiries!
+Relying only on directories means paying high commissions and sharing leads with competitors. We build complete turnkey setups for CCTV companies:
+👉 Customer Website (1-Click WhatsApp Quotes): https://atryasolutions.netlify.app/
+👉 Operations Admin (Technician &amp; AMC Dispatch): https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough this week? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP8" s="2" t="inlineStr">
         <is>
-          <t>Stop Losing Direct Google Customers</t>
+          <t>Direct Customer Website &amp; AMC Admin Panel for SPY HUB CCTV SALES AND SERVICES</t>
         </is>
       </c>
       <c r="AQ8" s="2" t="inlineStr">
         <is>
-          <t>Dear SPY HUB CCTV SALES AND SERVICES,
-Are you missing out on direct Google customers and paying high commissions to directories?
-Atrya Solutions builds complete digital systems for CCTV companies. Get a high-converting customer website with instant WhatsApp quotes (LIVE DEMO: https://atryasolutions.netlify.app/) and an operations panel for technician dispatch, AMC schedules, and warranty records (LIVE DEMO: https://atryasolutions.netlify.app/admin).
-This powerful combo brings you high-value inquiries directly and automates your field operations.
-Would you be open to a quick 10-15 minute walkthrough?
+          <t>Hi SPY HUB CCTV SALES AND SERVICES Team,
+I came across your CCTV business in Bengaluru and saw your positive customer ratings. However, I noticed that potential clients searching Google cannot find a direct website to request CCTV quotes.
+Relying solely on local directories means you share leads with 4–5 competitors and pay ongoing commissions.
+At Atrya Solutions, we build complete turnkey systems specifically for CCTV and security installers:
+1. Customer-Facing Website (captures direct leads with 1-click WhatsApp quotes):
+   👉 Demo: https://atryasolutions.netlify.app/
+2. Operations Admin Panel (tracks jobs, AMC maintenance contracts, and technician dispatch):
+   👉 Demo Admin: https://atryasolutions.netlify.app/admin
+We customize and deliver the complete setup in 48 hours.
+Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2149,7 +2175,7 @@
       </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919108896878?text=Hi%20CAMERAN%20Store%2C%0AI%20noticed%20you%20rely%20on%20directories%20for%20leads.%20You%E2%80%99re%20likely%20losing%20direct%20Google%20customers%20and%20paying%20heavy%20commissions.%20Atrya%E2%80%99s%20LIVE%20DEMO%20shows%20a%20high%E2%80%91converting%20website%20with%201%E2%80%91click%20WhatsApp%20quotes%20%2B%20an%20admin%20panel%20that%20automates%20tech%20dispatch%20%26%20AMC%20renewals.%20Can%20we%20schedule%20a%2010%E2%80%91min%20walkthrough%3F%0Ahttps%3A//atryasolutions.netlify.app/%0Ahttps%3A//atryasolutions.netlify.app/admin</t>
+          <t>https://wa.me/919108896878?text=Hi%20CAMERAN%20Store%2C%0ANoticed%20your%20security%20systems%20store%20in%20Bengaluru%20has%20strong%20footfall%2C%20but%20no%20dedicated%20web%20portal%20for%20wholesale%20and%20installer%20inquiries%21%0A%0AWe%20set%20up%20branded%20digital%20product%20catalogs%20with%20direct%20WhatsApp%20quote%20buttons%3A%0A%F0%9F%91%89%20Customer%20Website%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Warranty%20%26%20Technician%20Dispatch%20Admin%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AWorth%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T9" s="4" t="inlineStr"/>
@@ -2220,23 +2246,28 @@
       <c r="AO9" s="4" t="inlineStr">
         <is>
           <t>Hi CAMERAN Store,
-I noticed you rely on directories for leads. You’re likely losing direct Google customers and paying heavy commissions. Atrya’s LIVE DEMO shows a high‑converting website with 1‑click WhatsApp quotes + an admin panel that automates tech dispatch &amp; AMC renewals. Can we schedule a 10‑min walkthrough?
-https://atryasolutions.netlify.app/
-https://atryasolutions.netlify.app/admin</t>
+Noticed your security systems store in Bengaluru has strong footfall, but no dedicated web portal for wholesale and installer inquiries!
+We set up branded digital product catalogs with direct WhatsApp quote buttons:
+👉 Customer Website: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Worth a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP9" s="4" t="inlineStr">
         <is>
-          <t>Capture Direct Leads, Cut Commissions</t>
+          <t>Online Dealer Catalog &amp; Dispatch Panel for CAMERAN Store</t>
         </is>
       </c>
       <c r="AQ9" s="4" t="inlineStr">
         <is>
-          <t>Hi [First Name],
-I’ve observed that CAMERAN Store currently depends on directories for leads. That approach often funnels potential customers to competitors and incurs hefty commission fees on platforms like Justdial and IndiaMart.
-Atrya Solutions can instantly turn Google searches into high‑value inquiries with a custom website featuring 1‑click WhatsApp quote buttons and online lead forms. The LIVE DEMO here (https://atryasolutions.netlify.app/) shows exactly what we build for CCTV firms.
-Coupled with our Operations &amp; AMC Dispatch Admin panel (https://atryasolutions.netlify.app/admin), you’ll automate technician scheduling, warranty tracking, and service renewal alerts—saving time and boosting ROI.
-Would you have 10‑15 minutes for a quick walkthrough?
+          <t>Hi CAMERAN Store Management,
+I came across your security systems store in Bengaluru. While you have great local reputation, potential buyers searching Google for CCTV wholesale pricing and package installation cannot find an official portal.
+We build complete digital setups for security dealers:
+👉 Interactive Website with 1-click WhatsApp Quotes: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Could we connect for a brief 10-minute walkthrough this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2397,25 +2428,29 @@
       <c r="AN10" s="2" t="inlineStr"/>
       <c r="AO10" s="2" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions! 
-Crystal Technologies, are you losing direct Google customers to competitors and paying heavy commissions to Justdial/IndiaMart?
-We build turnkey digital systems for CCTV companies. Get a high-converting customer website with WhatsApp quote buttons AND an admin panel for job dispatch/AMC. 
-See LIVE DEMO: https://atryasolutions.netlify.app/ 
-Let's chat for 15 mins?</t>
+          <t>Hi Crystal Technologies team,
+Saw your IT &amp; networking hub in Bengaluru. Most IT dealers handle CCTV and AMC inquiries, but lose high-margin corporate clients because they don't have a direct quote catalog online.
+We build turnkey systems for IT &amp; CCTV hardware providers:
+👉 1-Click WhatsApp Quote Website: https://atryasolutions.netlify.app/
+👉 AMC Maintenance &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min demo? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP10" s="2" t="inlineStr">
         <is>
-          <t>Crystal Technologies: Stop Losing Direct Customers</t>
+          <t>Direct Corporate Leads &amp; AMC Panel for Crystal Technologies</t>
         </is>
       </c>
       <c r="AQ10" s="2" t="inlineStr">
         <is>
-          <t>Dear Crystal Technologies,
-Are you missing out on direct Google customers and paying high commissions to directories?
-Atrya Solutions builds complete digital systems for CCTV companies. Get a high-converting customer website with instant WhatsApp quotes (LIVE DEMO: https://atryasolutions.netlify.app/) AND an operations/AMC dispatch admin panel (LIVE DEMO: https://atryasolutions.netlify.app/admin).
-This combo helps you capture direct, high-value inquiries and automates technician &amp; AMC management.
-Would you be open to a quick 10-15 minute walkthrough?
+          <t>Hi Crystal Technologies Team,
+I came across your hardware &amp; networking hub in Bengaluru. Many IT firms handle CCTV and networking installations but lose high-margin corporate clients because they lack a dedicated website showcasing their solutions.
+We build turnkey systems for IT &amp; CCTV hardware providers:
+1. Instant WhatsApp Quote &amp; Product Catalog: https://atryasolutions.netlify.app/
+2. AMC Maintenance &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute demo to see how this brings direct inquiries without directory commissions?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2514,7 +2549,7 @@
       </c>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/918123405008?text=Hi%20%5BName%5D%2C%0AI%20noticed%20SHREE%20SUNDHA%20IT%20WORLD%20relies%20on%20directories%20for%20leads.%20You%E2%80%99re%20likely%20losing%20direct%20Google%20customers%20and%20paying%20heavy%20commissions.%0AAtrya%E2%80%99s%20LIVE%20DEMO%20shows%20a%20high%E2%80%91converting%20website%20with%201%E2%80%91click%20WhatsApp%20quote%20buttons%20%2B%20an%20Operations%20%26%20AMC%20admin%20panel%20that%20automates%20tech%20dispatch%20and%20service%20renewals.%0ACan%20we%20schedule%20a%2010%E2%80%9115%E2%80%AFmin%20walkthrough%3F%0AReply%20STOP%20and%20I%20won%27t%20contact%20you%20again.</t>
+          <t>https://wa.me/918123405008?text=Hi%20SHREE%20SUNDHA%20IT%20WORLD%2C%0ANoticed%20your%20security%20systems%20store%20in%20Bengaluru%20has%20strong%20footfall%2C%20but%20no%20dedicated%20web%20portal%20for%20wholesale%20and%20installer%20inquiries%21%0A%0AWe%20set%20up%20branded%20digital%20product%20catalogs%20with%20direct%20WhatsApp%20quote%20buttons%3A%0A%F0%9F%91%89%20Customer%20Website%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Warranty%20%26%20Technician%20Dispatch%20Admin%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AWorth%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr"/>
@@ -2584,24 +2619,29 @@
       <c r="AN11" s="4" t="inlineStr"/>
       <c r="AO11" s="4" t="inlineStr">
         <is>
-          <t>Hi [Name],
-I noticed SHREE SUNDHA IT WORLD relies on directories for leads. You’re likely losing direct Google customers and paying heavy commissions.
-Atrya’s LIVE DEMO shows a high‑converting website with 1‑click WhatsApp quote buttons + an Operations &amp; AMC admin panel that automates tech dispatch and service renewals.
-Can we schedule a 10‑15 min walkthrough?
-Reply STOP and I won't contact you again.</t>
+          <t>Hi SHREE SUNDHA IT WORLD,
+Noticed your security systems store in Bengaluru has strong footfall, but no dedicated web portal for wholesale and installer inquiries!
+We set up branded digital product catalogs with direct WhatsApp quote buttons:
+👉 Customer Website: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Worth a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP11" s="4" t="inlineStr">
         <is>
-          <t>Capture Direct Google Leads Instantly</t>
+          <t>Online Dealer Catalog &amp; Dispatch Panel for SHREE SUNDHA IT WORLD</t>
         </is>
       </c>
       <c r="AQ11" s="4" t="inlineStr">
         <is>
-          <t>Hi [Name],
-I’ve observed that SHREE SUNDHA IT WORLD currently depends on directories like Justdial for leads. This approach not only hands over high‑value Google customers to competitors but also incurs hefty commission fees.
-Atrya Solutions can turn that around with a turnkey, high‑converting website featuring instant 1‑click WhatsApp quote buttons, plus an Operations &amp; AMC Dispatch Admin panel that automates technician scheduling, warranty tracking, and service renewal alerts. See the LIVE DEMO here: https://atryasolutions.netlify.app/ and the admin panel here: https://atryasolutions.netlify.app/admin.
-Let’s discuss a quick 10‑15 minute walkthrough to show the ROI impact for your business.
+          <t>Hi SHREE SUNDHA IT WORLD Management,
+I came across your security systems store in Bengaluru. While you have great local reputation, potential buyers searching Google for CCTV wholesale pricing and package installation cannot find an official portal.
+We build complete digital setups for security dealers:
+👉 Interactive Website with 1-click WhatsApp Quotes: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Could we connect for a brief 10-minute walkthrough this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2700,7 +2740,7 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919845405646?text=Hi%20from%20Atrya%20Solutions%21%20%0A%0AKalyani%20Electronics%2C%20you%27re%20missing%20direct%20Google%20customers%20and%20paying%20high%20commissions%20without%20a%20website.%20%0A%0AOur%20system%20gives%20you%20direct%20WhatsApp%20inquiries%20AND%20automates%20technician/AMC%20management.%20%0A%0ASee%20a%20LIVE%20DEMO%3A%20https%3A//atryasolutions.netlify.app/%20%28Customer%20Site%29%20%26%20https%3A//atryasolutions.netlify.app/admin%20%28Admin%20Panel%29.%20%0A%0AReady%20for%20a%20quick%2015-min%20walkthrough%3F</t>
+          <t>https://wa.me/919845405646?text=Hi%20Kalyani%20electronics%2C%0ANoticed%20your%20security%20systems%20store%20in%20Bengaluru%20has%20strong%20footfall%2C%20but%20no%20dedicated%20web%20portal%20for%20wholesale%20and%20installer%20inquiries%21%0A%0AWe%20set%20up%20branded%20digital%20product%20catalogs%20with%20direct%20WhatsApp%20quote%20buttons%3A%0A%F0%9F%91%89%20Customer%20Website%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20Warranty%20%26%20Technician%20Dispatch%20Admin%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AWorth%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr"/>
@@ -2770,28 +2810,29 @@
       <c r="AN12" s="2" t="inlineStr"/>
       <c r="AO12" s="2" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions! 
-Kalyani Electronics, you're missing direct Google customers and paying high commissions without a website. 
-Our system gives you direct WhatsApp inquiries AND automates technician/AMC management. 
-See a LIVE DEMO: https://atryasolutions.netlify.app/ (Customer Site) &amp; https://atryasolutions.netlify.app/admin (Admin Panel). 
-Ready for a quick 15-min walkthrough?</t>
+          <t>Hi Kalyani electronics,
+Noticed your security systems store in Bengaluru has strong footfall, but no dedicated web portal for wholesale and installer inquiries!
+We set up branded digital product catalogs with direct WhatsApp quote buttons:
+👉 Customer Website: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Worth a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP12" s="2" t="inlineStr">
         <is>
-          <t>Stop Losing Google Customers, Kalyani!</t>
+          <t>Online Dealer Catalog &amp; Dispatch Panel for Kalyani electronics</t>
         </is>
       </c>
       <c r="AQ12" s="2" t="inlineStr">
         <is>
-          <t>Dear Kalyani Electronics Team,
-Without an official website, you're likely losing direct Google customers to competitors and paying heavy commissions to directories.
-Atrya Solutions offers a turnkey digital system to capture direct inquiries via WhatsApp and streamline your operations.
-See a LIVE DEMO of what we customize:
-*   Customer Website: https://atryasolutions.netlify.app/
-*   Operations &amp; AMC Dispatch Admin: https://atryasolutions.netlify.app/admin
-This combo gives you direct high-value customer inquiries and automates technician job dispatch, AMC schedules, and service renewals.
-Would you be open to a quick 10-15 minute walkthrough?
+          <t>Hi Kalyani electronics Management,
+I came across your security systems store in Bengaluru. While you have great local reputation, potential buyers searching Google for CCTV wholesale pricing and package installation cannot find an official portal.
+We build complete digital setups for security dealers:
+👉 Interactive Website with 1-click WhatsApp Quotes: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Could we connect for a brief 10-minute walkthrough this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2948,27 +2989,29 @@
       <c r="AN13" s="4" t="inlineStr"/>
       <c r="AO13" s="4" t="inlineStr">
         <is>
-          <t>Hi! Are you COST 2 COST SECURITY SYSTEMS in Bengaluru?
-Many CCTV businesses lose direct Google customers to competitors and pay huge commissions to Justdial/IndiaMart.
-We build turnkey systems to capture direct leads via WhatsApp and automate technician/AMC management.
-Would you be open to a 10-15 min demo?</t>
+          <t>Hi COST 2 COST SECURITY SYSTEMS,
+Noticed your security systems store in Bengaluru has strong footfall, but no dedicated web portal for wholesale and installer inquiries!
+We set up branded digital product catalogs with direct WhatsApp quote buttons:
+👉 Customer Website: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Worth a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP13" s="4" t="inlineStr">
         <is>
-          <t>Boost Leads, Automate Operations: COST 2 COST</t>
+          <t>Online Dealer Catalog &amp; Dispatch Panel for COST 2 COST SECURITY SYSTEMS</t>
         </is>
       </c>
       <c r="AQ13" s="4" t="inlineStr">
         <is>
-          <t>Dear COST 2 COST SECURITY SYSTEMS,
-I noticed you rely on directories, potentially missing direct Google customers and paying high commissions.
-We build custom digital systems to capture high-value inquiries directly via WhatsApp and streamline your field operations.
-See a LIVE DEMO of what we customize:
-Customer Website: https://atryasolutions.netlify.app/
-Operations &amp; AMC Dispatch Admin: https://atryasolutions.netlify.app/admin
-This combo helps you get direct leads and automates technician/AMC management.
-Would you be open to a quick 10-15 minute walkthrough?
+          <t>Hi COST 2 COST SECURITY SYSTEMS Management,
+I came across your security systems store in Bengaluru. While you have great local reputation, potential buyers searching Google for CCTV wholesale pricing and package installation cannot find an official portal.
+We build complete digital setups for security dealers:
+👉 Interactive Website with 1-click WhatsApp Quotes: https://atryasolutions.netlify.app/
+👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Could we connect for a brief 10-minute walkthrough this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3067,7 +3110,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/918278605168?text=Hi%20%5BName%5D%2C%0AI%20noticed%20Mega%20IT%20Hub%20relies%20on%20directories%20for%20leads.%20You%E2%80%99re%20missing%20direct%20Google%20customers%20and%20paying%20high%20commissions.%0ACheck%20our%20LIVE%20DEMO%3A%0ACustomer%20site%20%26%20WhatsApp%20quote%20button%20https%3A//atryasolutions.netlify.app/%0AAdmin%20panel%20for%20tech%20dispatch%20%26%20AMC%20https%3A//atryasolutions.netlify.app/admin%0ACan%20we%20schedule%20a%2010%E2%80%9115%E2%80%AFmin%20walkthrough%3F%0ABest%2C%0A%5BYour%20Name%5D</t>
+          <t>https://wa.me/918278605168?text=Hi%20Mega%20IT%20Hub%20team%2C%0ASaw%20your%20IT%20%26%20networking%20hub%20in%20Bengaluru.%20Most%20IT%20dealers%20handle%20CCTV%20and%20AMC%20inquiries%2C%20but%20lose%20high-margin%20corporate%20clients%20because%20they%20don%27t%20have%20a%20direct%20quote%20catalog%20online.%0A%0AWe%20build%20turnkey%20systems%20for%20IT%20%26%20CCTV%20hardware%20providers%3A%0A%F0%9F%91%89%201-Click%20WhatsApp%20Quote%20Website%3A%20https%3A//atryasolutions.netlify.app/%0A%F0%9F%91%89%20AMC%20Maintenance%20%26%20Technician%20Dispatch%20Admin%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20demo%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr"/>
@@ -3137,34 +3180,29 @@
       <c r="AN14" s="2" t="inlineStr"/>
       <c r="AO14" s="2" t="inlineStr">
         <is>
-          <t>Hi [Name],
-I noticed Mega IT Hub relies on directories for leads. You’re missing direct Google customers and paying high commissions.
-Check our LIVE DEMO:
-Customer site &amp; WhatsApp quote button https://atryasolutions.netlify.app/
-Admin panel for tech dispatch &amp; AMC https://atryasolutions.netlify.app/admin
-Can we schedule a 10‑15 min walkthrough?
-Best,
-[Your Name]</t>
+          <t>Hi Mega IT Hub team,
+Saw your IT &amp; networking hub in Bengaluru. Most IT dealers handle CCTV and AMC inquiries, but lose high-margin corporate clients because they don't have a direct quote catalog online.
+We build turnkey systems for IT &amp; CCTV hardware providers:
+👉 1-Click WhatsApp Quote Website: https://atryasolutions.netlify.app/
+👉 AMC Maintenance &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min demo? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP14" s="2" t="inlineStr">
         <is>
-          <t>Capture Direct Google Leads</t>
+          <t>Direct Corporate Leads &amp; AMC Panel for Mega IT Hub</t>
         </is>
       </c>
       <c r="AQ14" s="2" t="inlineStr">
         <is>
-          <t>Hi [Name],
-I’ve noticed Mega IT Hub doesn’t have an official website and relies on directories like Justdial. That means you’re losing direct Google customers and paying hefty commissions for each lead.
-We specialize in building turnkey digital systems for CCTV firms. Our LIVE DEMO shows exactly what we can launch for you:
-- Customer website with instant 1‑click WhatsApp quote buttons &amp; online lead forms: https://atryasolutions.netlify.app/
-- Operations &amp; AMC Dispatch admin panel that automates technician scheduling, warranty tracking, and service renewal alerts: https://atryasolutions.netlify.app/admin
-The combo delivers high‑value inquiries straight to your WhatsApp and streamlines field operations, boosting ROI instantly.
-Can we set up a quick 10‑15 minute walkthrough this week?
+          <t>Hi Mega IT Hub Team,
+I came across your hardware &amp; networking hub in Bengaluru. Many IT firms handle CCTV and networking installations but lose high-margin corporate clients because they lack a dedicated website showcasing their solutions.
+We build turnkey systems for IT &amp; CCTV hardware providers:
+1. Instant WhatsApp Quote &amp; Product Catalog: https://atryasolutions.netlify.app/
+2. AMC Maintenance &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute demo to see how this brings direct inquiries without directory commissions?
 Best regards,
-[Your Name]
-[Your Position]
-Atrya Solutions
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3263,7 +3301,7 @@
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919353219617?text=Hi%20from%20Atrya%20Solutions%21%20Your%20website%2C%20eyevista.in%2C%20isn%27t%20secure%20%28HTTPS%29%20and%20shows%20a%20403%20error%2C%20losing%20potential%20customers.%20We%20build%20secure%2C%20mobile-friendly%20sites%20with%20direct%20WhatsApp/enquiry%20forms%20to%20capture%20leads.%20We%20also%20offer%20an%20admin%20panel%20for%20technician/AMC%20management.%20Let%27s%20fix%20this%20and%20boost%20your%20business%21</t>
+          <t>https://wa.me/919353219617?text=Hi%20Eye%20Vista%20Electronic%20Security%20Solutions%2C%0AChecked%20your%20website%20%28eyevista.in%29%20in%20Bengaluru%20and%20noticed%20it%27s%20currently%20showing%20an%20issue%20%28not%20served%20over%20HTTPS%20%28insecure%20connection%29%3B%20HTTP%20error%20403%3B%20not%20mobile-friendly%20%28missing%20viewport%20tag%29%3B%20no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29%2C%20causing%20potential%20customers%20to%20bounce%21%0A%0AWe%20build%20fast%2C%20secure%20mobile%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AWe%27re%20offering%20a%20free%20revamp%20to%20get%20your%20site%20back%20to%20converting%20leads.%0A%0AOpen%20for%20a%20quick%2010-min%20chat%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T15" s="4" t="inlineStr"/>
@@ -3341,20 +3379,29 @@
       <c r="AN15" s="4" t="inlineStr"/>
       <c r="AO15" s="4" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions! Your website, eyevista.in, isn't secure (HTTPS) and shows a 403 error, losing potential customers. We build secure, mobile-friendly sites with direct WhatsApp/enquiry forms to capture leads. We also offer an admin panel for technician/AMC management. Let's fix this and boost your business!</t>
+          <t>Hi Eye Vista Electronic Security Solutions,
+Checked your website (eyevista.in) in Bengaluru and noticed it's currently showing an issue (not served over HTTPS (insecure connection); HTTP error 403; not mobile-friendly (missing viewport tag); no online enquiry or quote form; no direct WhatsApp contact widget), causing potential customers to bounce!
+We build fast, secure mobile sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+We're offering a free revamp to get your site back to converting leads.
+Open for a quick 10-min chat? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP15" s="4" t="inlineStr">
         <is>
-          <t>Free Website Revamp for Eye Vista</t>
+          <t>Fixing Eye Vista Electronic Security Solutions website (not served over HTTPS (insecure connecti) + Free Revamp</t>
         </is>
       </c>
       <c r="AQ15" s="4" t="inlineStr">
         <is>
-          <t>Dear Eye Vista Team,
-Your website, eyevista.in, currently has an insecure connection (HTTP error 403) and isn't mobile-friendly, likely costing you direct customer inquiries.
-At Atrya Solutions, we specialize in building secure, high-converting websites with instant WhatsApp quote buttons and online forms to capture direct Google customers. We also offer an operations panel for technician dispatch and AMC management.
-Let's discuss a free revamp to secure your site and boost your leads. Would you be open to a quick 10-15 minute walkthrough?
+          <t>Hi Eye Vista Electronic Security Solutions Team,
+I was looking up security providers in Bengaluru and tried visiting your website (eyevista.in).
+I noticed visitors are running into an issue: not served over HTTPS (insecure connection); HTTP error 403; not mobile-friendly (missing viewport tag); no online enquiry or quote form; no direct WhatsApp contact widget. When customers see an error or security warning, they immediately go to a competitor.
+At Atrya Solutions, we build high-converting websites for CCTV &amp; security dealers:
+👉 Live Demo: https://atryasolutions.netlify.app/
+👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
+We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3523,24 +3570,29 @@
       <c r="AN16" s="2" t="inlineStr"/>
       <c r="AO16" s="2" t="inlineStr">
         <is>
-          <t>Hi CP Plus World Store team,
-I noticed your site returns a 403 error and isn’t mobile‑friendly (no viewport tag), missing WhatsApp quote widget. We can revamp it for free and add a live demo of a high‑converting website + admin panel:
-Customer site demo: https://atryasolutions.netlify.app/
-Admin demo: https://atryasolutions.netlify.app/admin
-Can we schedule a 10‑15 min walkthrough?</t>
+          <t>Hi CP Plus World Store,
+Checked your website (stores.cpplusworld.com) in Bengaluru and noticed it's currently showing an issue (HTTP error 403; not mobile-friendly (missing viewport tag); no online enquiry or quote form; no direct WhatsApp contact widget), causing potential customers to bounce!
+We build fast, secure mobile sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+We're offering a free revamp to get your site back to converting leads.
+Open for a quick 10-min chat? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP16" s="2" t="inlineStr">
         <is>
-          <t>Free Site Revamp + WhatsApp Leads</t>
+          <t>Fixing CP Plus World Store website (HTTP error 403; not mobile-friendly (mis) + Free Revamp</t>
         </is>
       </c>
       <c r="AQ16" s="2" t="inlineStr">
         <is>
-          <t>Hi CP Plus World Store,
-During our audit we found your website returns an HTTP 403 error, lacks a mobile viewport tag, and has no online enquiry or WhatsApp quote widget. These issues block direct Google customers and drive them to competitors.
-Atrya can rebuild your site at no cost, adding a 1‑click WhatsApp quote button and an online lead form that converts visitors into high‑value inquiries. See a live custom demo here: https://atryasolutions.netlify.app/ and our Operations &amp; AMC admin panel here: https://atryasolutions.netlify.app/admin.
-Let’s discuss a quick 10‑15 minute walkthrough to show the ROI impact.
+          <t>Hi CP Plus World Store Team,
+I was looking up security providers in Bengaluru and tried visiting your website (stores.cpplusworld.com).
+I noticed visitors are running into an issue: HTTP error 403; not mobile-friendly (missing viewport tag); no online enquiry or quote form; no direct WhatsApp contact widget. When customers see an error or security warning, they immediately go to a competitor.
+At Atrya Solutions, we build high-converting websites for CCTV &amp; security dealers:
+👉 Live Demo: https://atryasolutions.netlify.app/
+👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
+We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3639,7 +3691,7 @@
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/918050877007?text=Hi%20Mega%20CCTV%20World%2C%0AYour%20site%20isn%E2%80%99t%20secure%20%28no%20HTTPS%29%20and%20shows%20a%20404%20error%2C%20plus%20it%20isn%E2%80%99t%20mobile%E2%80%91friendly.%20We%20can%20give%20you%20a%20fresh%2C%20HTTPS%E2%80%91protected%20website%20with%20instant%20WhatsApp%20quote%20buttons%20and%20a%20full%20admin%20panel%20%E2%80%93%20all%20at%20zero%20cost%20to%20revamp.%0ASee%20LIVE%20DEMO%3A%20https%3A//atryasolutions.netlify.app/%0AAdmin%20Demo%3A%20https%3A//atryasolutions.netlify.app/admin%0ACan%20we%20schedule%20a%2010%E2%80%9115%E2%80%AFmin%20call%3F</t>
+          <t>https://wa.me/918050877007?text=Hi%20Mega%20CCTV%20World%2C%0AChecked%20your%20website%20%28business.google.com%29%20in%20Bengaluru%20and%20noticed%20it%27s%20currently%20showing%20an%20issue%20%28not%20served%20over%20HTTPS%20%28insecure%20connection%29%3B%20HTTP%20error%20404%3B%20not%20mobile-friendly%20%28missing%20viewport%20tag%29%3B%20no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29%2C%20causing%20potential%20customers%20to%20bounce%21%0A%0AWe%20build%20fast%2C%20secure%20mobile%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AWe%27re%20offering%20a%20free%20revamp%20to%20get%20your%20site%20back%20to%20converting%20leads.%0A%0AOpen%20for%20a%20quick%2010-min%20chat%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T17" s="4" t="inlineStr"/>
@@ -3718,25 +3770,28 @@
       <c r="AO17" s="4" t="inlineStr">
         <is>
           <t>Hi Mega CCTV World,
-Your site isn’t secure (no HTTPS) and shows a 404 error, plus it isn’t mobile‑friendly. We can give you a fresh, HTTPS‑protected website with instant WhatsApp quote buttons and a full admin panel – all at zero cost to revamp.
-See LIVE DEMO: https://atryasolutions.netlify.app/
-Admin Demo: https://atryasolutions.netlify.app/admin
-Can we schedule a 10‑15 min call?</t>
+Checked your website (business.google.com) in Bengaluru and noticed it's currently showing an issue (not served over HTTPS (insecure connection); HTTP error 404; not mobile-friendly (missing viewport tag); no online enquiry or quote form; no direct WhatsApp contact widget), causing potential customers to bounce!
+We build fast, secure mobile sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+We're offering a free revamp to get your site back to converting leads.
+Open for a quick 10-min chat? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP17" s="4" t="inlineStr">
         <is>
-          <t>Secure Site &amp; Boost Leads</t>
+          <t>Fixing Mega CCTV World website (not served over HTTPS (insecure connecti) + Free Revamp</t>
         </is>
       </c>
       <c r="AQ17" s="4" t="inlineStr">
         <is>
-          <t>Hi [Name],
-I noticed Mega CCTV World’s website is not served over HTTPS, returns a 404 error and lacks mobile‑friendly design – all of which deter direct Google customers and expose you to security risks.
-Atrya Solutions can rebuild it as a high‑converting, secure site with instant 1‑click WhatsApp quote buttons and a dedicated Operations &amp; AMC Dispatch admin panel, at no cost for the revamp.
-Check the LIVE DEMO of what we deliver: https://atryasolutions.netlify.app/
-Admin panel demo: https://atryasolutions.netlify.app/admin
-Let’s discuss a quick 10‑15 minute walkthrough to show the ROI.
+          <t>Hi Mega CCTV World Team,
+I was looking up security providers in Bengaluru and tried visiting your website (business.google.com).
+I noticed visitors are running into an issue: not served over HTTPS (insecure connection); HTTP error 404; not mobile-friendly (missing viewport tag); no online enquiry or quote form; no direct WhatsApp contact widget. When customers see an error or security warning, they immediately go to a competitor.
+At Atrya Solutions, we build high-converting websites for CCTV &amp; security dealers:
+👉 Live Demo: https://atryasolutions.netlify.app/
+👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
+We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3835,7 +3890,7 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/917598111110?text=Hi%20TECHLOGICS%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%20Bengaluru%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28SSL%20certificate%20expired/invalid%20%28security%20warning%29%3B%20HTTP%20error%20409%3B%20not%20mobile-friendly%20%28missing%20viewport%20tag%29%3B%20no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+          <t>https://wa.me/917598111110?text=Hi%20TECHLOGICS%2C%0AChecked%20your%20website%20%28techlogics.in%29%20in%20Bengaluru%20and%20noticed%20it%27s%20currently%20showing%20an%20issue%20%28SSL%20certificate%20expired/invalid%20%28security%20warning%29%3B%20HTTP%20error%20409%3B%20not%20mobile-friendly%20%28missing%20viewport%20tag%29%3B%20no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29%2C%20causing%20potential%20customers%20to%20bounce%21%0A%0AWe%20build%20fast%2C%20secure%20mobile%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AWe%27re%20offering%20a%20free%20revamp%20to%20get%20your%20site%20back%20to%20converting%20leads.%0A%0AOpen%20for%20a%20quick%2010-min%20chat%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr"/>
@@ -3914,24 +3969,28 @@
       <c r="AO18" s="2" t="inlineStr">
         <is>
           <t>Hi TECHLOGICS,
-Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (SSL certificate expired/invalid (security warning); HTTP error 409; not mobile-friendly (missing viewport tag); no online enquiry or quote form; no direct WhatsApp contact widget).
-We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
-Open to a quick demo?</t>
+Checked your website (techlogics.in) in Bengaluru and noticed it's currently showing an issue (SSL certificate expired/invalid (security warning); HTTP error 409; not mobile-friendly (missing viewport tag); no online enquiry or quote form; no direct WhatsApp contact widget), causing potential customers to bounce!
+We build fast, secure mobile sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+We're offering a free revamp to get your site back to converting leads.
+Open for a quick 10-min chat? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP18" s="2" t="inlineStr">
         <is>
-          <t>Improving CCTV quote enquiries for TECHLOGICS</t>
+          <t>Fixing TECHLOGICS website (SSL certificate expired/invalid (securit) + Free Revamp</t>
         </is>
       </c>
       <c r="AQ18" s="2" t="inlineStr">
         <is>
-          <t>Hi TECHLOGICS,
-I was looking up CCTV providers in Bengaluru and checked your website.
-I noticed a couple of areas that might be reducing your lead conversion: SSL certificate expired/invalid (security warning); HTTP error 409; not mobile-friendly (missing viewport tag); no online enquiry or quote form; no direct WhatsApp contact widget.
-At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
-Live demo: https://atryasolutions.netlify.app/
-Would you be interested in a brief 10-minute walkthrough?
+          <t>Hi TECHLOGICS Team,
+I was looking up security providers in Bengaluru and tried visiting your website (techlogics.in).
+I noticed visitors are running into an issue: SSL certificate expired/invalid (security warning); HTTP error 409; not mobile-friendly (missing viewport tag); no online enquiry or quote form; no direct WhatsApp contact widget. When customers see an error or security warning, they immediately go to a competitor.
+At Atrya Solutions, we build high-converting websites for CCTV &amp; security dealers:
+👉 Live Demo: https://atryasolutions.netlify.app/
+👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
+We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -4030,7 +4089,7 @@
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919008280000?text=Hi%20from%20Atrya%20Solutions%21%20Your%20website%2C%20http%3A//www.spectrumcontracting.in/%2C%20seems%20to%20be%20facing%20an%20HTTP%20404%20error%20and%20isn%27t%20mobile-friendly.%20We%20help%20CCTV%20companies%20like%20yours%20in%20Bengaluru%20get%20direct%20customer%20inquiries%20via%20WhatsApp%20and%20streamline%20operations.%20Let%27s%20fix%20this%20for%20you%21%20We%20offer%20a%20free%20revamp.%20Reply%20STOP%20to%20unsubscribe.</t>
+          <t>https://wa.me/919008280000?text=Hi%20Spectrum%20Technologies%2C%0AChecked%20your%20website%20%28spectrumcontracting.in%29%20in%20Bengaluru%20and%20noticed%20it%27s%20currently%20showing%20an%20issue%20%28HTTP%20error%20404%3B%20not%20mobile-friendly%20%28missing%20viewport%20tag%29%3B%20no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29%2C%20causing%20potential%20customers%20to%20bounce%21%0A%0AWe%20build%20fast%2C%20secure%20mobile%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AWe%27re%20offering%20a%20free%20revamp%20to%20get%20your%20site%20back%20to%20converting%20leads.%0A%0AOpen%20for%20a%20quick%2010-min%20chat%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T19" s="4" t="inlineStr"/>
@@ -4108,21 +4167,29 @@
       <c r="AN19" s="4" t="inlineStr"/>
       <c r="AO19" s="4" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions! Your website, http://www.spectrumcontracting.in/, seems to be facing an HTTP 404 error and isn't mobile-friendly. We help CCTV companies like yours in Bengaluru get direct customer inquiries via WhatsApp and streamline operations. Let's fix this for you! We offer a free revamp. Reply STOP to unsubscribe.</t>
+          <t>Hi Spectrum Technologies,
+Checked your website (spectrumcontracting.in) in Bengaluru and noticed it's currently showing an issue (HTTP error 404; not mobile-friendly (missing viewport tag); no online enquiry or quote form; no direct WhatsApp contact widget), causing potential customers to bounce!
+We build fast, secure mobile sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+We're offering a free revamp to get your site back to converting leads.
+Open for a quick 10-min chat? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP19" s="4" t="inlineStr">
         <is>
-          <t>Free Website Revamp for Spectrum Technologies</t>
+          <t>Fixing Spectrum Technologies website (HTTP error 404; not mobile-friendly (mis) + Free Revamp</t>
         </is>
       </c>
       <c r="AQ19" s="4" t="inlineStr">
         <is>
-          <t>Dear Spectrum Technologies Team,
-We noticed your website, http://www.spectrumcontracting.in/, is currently showing an HTTP 404 error and isn't optimized for mobile. This can impact your online presence and customer trust.
-At Atrya Solutions, we specialize in building high-converting digital systems for CCTV companies. We can revamp your site to capture direct Google customers via WhatsApp and online forms, eliminating directory commissions.
-See a LIVE DEMO of what we customize: Customer Website: https://atryasolutions.netlify.app/
-We'd love to offer a free revamp and show you how our Operations &amp; AMC Dispatch Admin (LIVE DEMO: https://atryasolutions.netlify.app/admin) can automate your field technician and AMC management. Would you be open to a quick 10-15 minute walkthrough?
+          <t>Hi Spectrum Technologies Team,
+I was looking up security providers in Bengaluru and tried visiting your website (spectrumcontracting.in).
+I noticed visitors are running into an issue: HTTP error 404; not mobile-friendly (missing viewport tag); no online enquiry or quote form; no direct WhatsApp contact widget. When customers see an error or security warning, they immediately go to a competitor.
+At Atrya Solutions, we build high-converting websites for CCTV &amp; security dealers:
+👉 Live Demo: https://atryasolutions.netlify.app/
+👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
+We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -4221,7 +4288,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919967400942?text=Hi%20PR%20Technology%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%2050%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28website%20unreachable%20%28ConnectionError%29%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+          <t>https://wa.me/919967400942?text=Hi%20PR%20Technology%2C%0AChecked%20your%20website%20%28prtechnologycompany.com%29%20in%20Mumbai%20and%20noticed%20it%27s%20currently%20showing%20an%20issue%20%28website%20unreachable%20%28ConnectionError%29%29%2C%20causing%20potential%20customers%20to%20bounce%21%0A%0AWe%20build%20fast%2C%20secure%20mobile%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AWe%27re%20offering%20a%20free%20revamp%20to%20get%20your%20site%20back%20to%20converting%20leads.%0A%0AOpen%20for%20a%20quick%2010-min%20chat%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr"/>
@@ -4300,24 +4367,28 @@
       <c r="AO20" s="2" t="inlineStr">
         <is>
           <t>Hi PR Technology,
-Took a look at your CCTV website in 50 and noticed a few things holding back customer enquiries (website unreachable (ConnectionError)).
-We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
-Open to a quick demo?</t>
+Checked your website (prtechnologycompany.com) in Mumbai and noticed it's currently showing an issue (website unreachable (ConnectionError)), causing potential customers to bounce!
+We build fast, secure mobile sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+We're offering a free revamp to get your site back to converting leads.
+Open for a quick 10-min chat? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP20" s="2" t="inlineStr">
         <is>
-          <t>Improving CCTV quote enquiries for PR Technology</t>
+          <t>Fixing PR Technology website (website unreachable (ConnectionError)) + Free Revamp</t>
         </is>
       </c>
       <c r="AQ20" s="2" t="inlineStr">
         <is>
-          <t>Hi PR Technology,
-I was looking up CCTV providers in 50 and checked your website.
-I noticed a couple of areas that might be reducing your lead conversion: website unreachable (ConnectionError).
-At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
-Live demo: https://atryasolutions.netlify.app/
-Would you be interested in a brief 10-minute walkthrough?
+          <t>Hi PR Technology Team,
+I was looking up security providers in Mumbai and tried visiting your website (prtechnologycompany.com).
+I noticed visitors are running into an issue: website unreachable (ConnectionError). When customers see an error or security warning, they immediately go to a competitor.
+At Atrya Solutions, we build high-converting websites for CCTV &amp; security dealers:
+👉 Live Demo: https://atryasolutions.netlify.app/
+👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
+We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -4416,7 +4487,7 @@
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919849242004?text=Hi%20Super-V-Tech%20Zone%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%2050%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28website%20unreachable%20%28ConnectionError%29%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+          <t>https://wa.me/919849242004?text=Hi%20Super-V-Tech%20Zone%2C%0AChecked%20your%20website%20%28supervtechzone.com%29%20in%20Hyderabad%20and%20noticed%20it%27s%20currently%20showing%20an%20issue%20%28website%20unreachable%20%28ConnectionError%29%29%2C%20causing%20potential%20customers%20to%20bounce%21%0A%0AWe%20build%20fast%2C%20secure%20mobile%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AWe%27re%20offering%20a%20free%20revamp%20to%20get%20your%20site%20back%20to%20converting%20leads.%0A%0AOpen%20for%20a%20quick%2010-min%20chat%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T21" s="4" t="inlineStr"/>
@@ -4495,24 +4566,28 @@
       <c r="AO21" s="4" t="inlineStr">
         <is>
           <t>Hi Super-V-Tech Zone,
-Took a look at your CCTV website in 50 and noticed a few things holding back customer enquiries (website unreachable (ConnectionError)).
-We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
-Open to a quick demo?</t>
+Checked your website (supervtechzone.com) in Hyderabad and noticed it's currently showing an issue (website unreachable (ConnectionError)), causing potential customers to bounce!
+We build fast, secure mobile sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+We're offering a free revamp to get your site back to converting leads.
+Open for a quick 10-min chat? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP21" s="4" t="inlineStr">
         <is>
-          <t>Improving CCTV quote enquiries for Super-V-Tech Zone</t>
+          <t>Fixing Super-V-Tech Zone website (website unreachable (ConnectionError)) + Free Revamp</t>
         </is>
       </c>
       <c r="AQ21" s="4" t="inlineStr">
         <is>
-          <t>Hi Super-V-Tech Zone,
-I was looking up CCTV providers in 50 and checked your website.
-I noticed a couple of areas that might be reducing your lead conversion: website unreachable (ConnectionError).
-At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
-Live demo: https://atryasolutions.netlify.app/
-Would you be interested in a brief 10-minute walkthrough?
+          <t>Hi Super-V-Tech Zone Team,
+I was looking up security providers in Hyderabad and tried visiting your website (supervtechzone.com).
+I noticed visitors are running into an issue: website unreachable (ConnectionError). When customers see an error or security warning, they immediately go to a competitor.
+At Atrya Solutions, we build high-converting websites for CCTV &amp; security dealers:
+👉 Live Demo: https://atryasolutions.netlify.app/
+👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
+We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -4611,7 +4686,7 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919686954889?text=Hi%20CCTV%20SHOP%20IN%20team%2C%0A%0AI%20noticed%20your%20website%20https%3A//cctv-shop.in/%20is%20currently%20unreachable%20%28ConnectionError%29.%20A%20broken%20site%20means%20missed%20Google%20leads%20and%20lost%20revenue.%0A%0AWe%20specialize%20in%20launching%20secure%2C%20high%E2%80%91converting%20sites%20with%20instant%201%E2%80%91click%20WhatsApp%20quote%20buttons.%20See%20a%20live%20demo%3A%20https%3A//atryasolutions.netlify.app/%20and%20our%20admin%20panel%3A%20https%3A//atryasolutions.netlify.app/admin.%0A%0ACan%20we%20schedule%20a%2010%E2%80%9115%E2%80%AFmin%20free%20revamp%20walkthrough%3F</t>
+          <t>https://wa.me/919686954889?text=Hi%20CCTV%20SHOP%20IN%2C%0AChecked%20your%20website%20%28cctv-shop.in%29%20in%20Bengaluru%20and%20noticed%20it%27s%20currently%20showing%20an%20issue%20%28website%20unreachable%20%28ConnectionError%29%29%2C%20causing%20potential%20customers%20to%20bounce%21%0A%0AWe%20build%20fast%2C%20secure%20mobile%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AWe%27re%20offering%20a%20free%20revamp%20to%20get%20your%20site%20back%20to%20converting%20leads.%0A%0AOpen%20for%20a%20quick%2010-min%20chat%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr"/>
@@ -4689,25 +4764,29 @@
       <c r="AN22" s="2" t="inlineStr"/>
       <c r="AO22" s="2" t="inlineStr">
         <is>
-          <t>Hi CCTV SHOP IN team,
-I noticed your website https://cctv-shop.in/ is currently unreachable (ConnectionError). A broken site means missed Google leads and lost revenue.
-We specialize in launching secure, high‑converting sites with instant 1‑click WhatsApp quote buttons. See a live demo: https://atryasolutions.netlify.app/ and our admin panel: https://atryasolutions.netlify.app/admin.
-Can we schedule a 10‑15 min free revamp walkthrough?</t>
+          <t>Hi CCTV SHOP IN,
+Checked your website (cctv-shop.in) in Bengaluru and noticed it's currently showing an issue (website unreachable (ConnectionError)), causing potential customers to bounce!
+We build fast, secure mobile sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+We're offering a free revamp to get your site back to converting leads.
+Open for a quick 10-min chat? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP22" s="2" t="inlineStr">
         <is>
-          <t>Fix Your Site, Capture Leads</t>
+          <t>Fixing CCTV SHOP IN website (website unreachable (ConnectionError)) + Free Revamp</t>
         </is>
       </c>
       <c r="AQ22" s="2" t="inlineStr">
         <is>
-          <t>Hello CCTV SHOP IN,
-During our quick audit, we found that https://cctv-shop.in/ is currently unreachable (ConnectionError). A non‑functional site not only harms your brand but also diverts direct Google customers to competitors and forces you to rely on costly directories.
-Atrya Solutions builds secure, high‑converting websites with instant 1‑click WhatsApp quote buttons, plus an Operations &amp; AMC Dispatch admin panel that automates technician scheduling and service renewals. You can view the exact experience we deliver here:
-- Customer website demo: https://atryasolutions.netlify.app/
-- Admin panel demo: https://atryasolutions.netlify.app/admin
-We’d love to offer a free revamp and walk you through the solution in a 10‑15 minute call. Let me know a convenient time.
+          <t>Hi CCTV SHOP IN Team,
+I was looking up security providers in Bengaluru and tried visiting your website (cctv-shop.in).
+I noticed visitors are running into an issue: website unreachable (ConnectionError). When customers see an error or security warning, they immediately go to a competitor.
+At Atrya Solutions, we build high-converting websites for CCTV &amp; security dealers:
+👉 Live Demo: https://atryasolutions.netlify.app/
+👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
+We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -4806,7 +4885,7 @@
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919353308823?text=Hi%20from%20Atrya%20Solutions%21%0A%0AWe%20noticed%20your%20website%2C%20hmitworld.com%2C%20is%20currently%20unreachable.%20This%20means%20potential%20customers%20can%27t%20find%20you%20online.%0A%0AWe%20specialize%20in%20building%20robust%20digital%20systems%20for%20CCTV%20companies.%20Let%20us%20help%20you%20get%20back%20online%20and%20capture%20direct%20leads.%0A%0ASee%20our%20LIVE%20DEMO%3A%20https%3A//atryasolutions.netlify.app/%0A%0AWant%20a%20quick%2015-min%20chat%3F</t>
+          <t>https://wa.me/919353308823?text=Hi%20HM%20IT%20WORLD%2C%0AChecked%20your%20website%20%28hmitworld.com%29%20in%20Bengaluru%20and%20noticed%20it%27s%20currently%20showing%20an%20issue%20%28website%20unreachable%20%28ConnectionError%29%29%2C%20causing%20potential%20customers%20to%20bounce%21%0A%0AWe%20build%20fast%2C%20secure%20mobile%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AWe%27re%20offering%20a%20free%20revamp%20to%20get%20your%20site%20back%20to%20converting%20leads.%0A%0AOpen%20for%20a%20quick%2010-min%20chat%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr"/>
@@ -4884,27 +4963,29 @@
       <c r="AN23" s="4" t="inlineStr"/>
       <c r="AO23" s="4" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions!
-We noticed your website, hmitworld.com, is currently unreachable. This means potential customers can't find you online.
-We specialize in building robust digital systems for CCTV companies. Let us help you get back online and capture direct leads.
-See our LIVE DEMO: https://atryasolutions.netlify.app/
-Want a quick 15-min chat?</t>
+          <t>Hi HM IT WORLD,
+Checked your website (hmitworld.com) in Bengaluru and noticed it's currently showing an issue (website unreachable (ConnectionError)), causing potential customers to bounce!
+We build fast, secure mobile sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+We're offering a free revamp to get your site back to converting leads.
+Open for a quick 10-min chat? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP23" s="4" t="inlineStr">
         <is>
-          <t>Your Website is Unreachable: Free Revamp?</t>
+          <t>Fixing HM IT WORLD website (website unreachable (ConnectionError)) + Free Revamp</t>
         </is>
       </c>
       <c r="AQ23" s="4" t="inlineStr">
         <is>
-          <t>Dear HM IT WORLD Team,
-We noticed your website, hmitworld.com, is currently unreachable. This can lead to lost customer inquiries and impact your online presence.
-At Atrya Solutions, we build turnkey digital systems for CCTV companies. We can help you fix this and launch a high-converting website to capture direct Google customers.
-Check out our LIVE DEMO of what we customize and launch:
-Customer Website: https://atryasolutions.netlify.app/
-Operations &amp; AMC Dispatch Admin: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-15 minute walkthrough to discuss a free revamp?
+          <t>Hi HM IT WORLD Team,
+I was looking up security providers in Bengaluru and tried visiting your website (hmitworld.com).
+I noticed visitors are running into an issue: website unreachable (ConnectionError). When customers see an error or security warning, they immediately go to a competitor.
+At Atrya Solutions, we build high-converting websites for CCTV &amp; security dealers:
+👉 Live Demo: https://atryasolutions.netlify.app/
+👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
+We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -5003,7 +5084,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919886489145?text=Hi%20Godrej%20CCTV%2C%20your%20website%20seems%20to%20be%20down.%20This%20means%20potential%20customers%20can%27t%20find%20you%20online.%0A%0AWe%20offer%20a%20free%20revamp%20to%20get%20you%20back%20on%20track%2C%20plus%20a%20system%20to%20capture%20direct%20leads%20via%20WhatsApp%20and%20automate%20technician%20dispatch.%0A%0ASee%20our%20LIVE%20DEMOs%3A%0ACustomer%20Website%3A%20https%3A//atryasolutions.netlify.app/%0AAdmin%20Panel%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AWould%20you%20be%20open%20to%20a%20quick%2015-min%20chat%3F</t>
+          <t>https://wa.me/919886489145?text=Hi%20Godrej%20CCTV%20Bangalore%2C%0AChecked%20your%20website%20%28godrejcctv.net%29%20in%20Bengaluru%20and%20noticed%20it%27s%20currently%20showing%20an%20issue%20%28website%20unreachable%20%28ConnectionError%29%29%2C%20causing%20potential%20customers%20to%20bounce%21%0A%0AWe%20build%20fast%2C%20secure%20mobile%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AWe%27re%20offering%20a%20free%20revamp%20to%20get%20your%20site%20back%20to%20converting%20leads.%0A%0AOpen%20for%20a%20quick%2010-min%20chat%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr"/>
@@ -5081,28 +5162,29 @@
       <c r="AN24" s="2" t="inlineStr"/>
       <c r="AO24" s="2" t="inlineStr">
         <is>
-          <t>Hi Godrej CCTV, your website seems to be down. This means potential customers can't find you online.
-We offer a free revamp to get you back on track, plus a system to capture direct leads via WhatsApp and automate technician dispatch.
-See our LIVE DEMOs:
-Customer Website: https://atryasolutions.netlify.app/
-Admin Panel: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 15-min chat?</t>
+          <t>Hi Godrej CCTV Bangalore,
+Checked your website (godrejcctv.net) in Bengaluru and noticed it's currently showing an issue (website unreachable (ConnectionError)), causing potential customers to bounce!
+We build fast, secure mobile sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
+We're offering a free revamp to get your site back to converting leads.
+Open for a quick 10-min chat? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP24" s="2" t="inlineStr">
         <is>
-          <t>Free Website Revamp + Direct Leads</t>
+          <t>Fixing Godrej CCTV Bangalore website (website unreachable (ConnectionError)) + Free Revamp</t>
         </is>
       </c>
       <c r="AQ24" s="2" t="inlineStr">
         <is>
-          <t>Dear Godrej CCTV Bangalore,
-We noticed your website, godrejcctv.net, is currently unreachable. This can significantly impact your customer acquisition and brand reputation.
-At Atrya Solutions, we offer a free revamp to fix this. We'll also equip you with a high-converting website to capture direct Google customers via WhatsApp, eliminating directory commissions.
-Our system also includes an Admin Panel for efficient technician dispatch and AMC management. See LIVE DEMOs:
-Customer Website: https://atryasolutions.netlify.app/
-Operations &amp; AMC Dispatch Admin: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-15 minute walkthrough?
+          <t>Hi Godrej CCTV Bangalore Team,
+I was looking up security providers in Bengaluru and tried visiting your website (godrejcctv.net).
+I noticed visitors are running into an issue: website unreachable (ConnectionError). When customers see an error or security warning, they immediately go to a competitor.
+At Atrya Solutions, we build high-converting websites for CCTV &amp; security dealers:
+👉 Live Demo: https://atryasolutions.netlify.app/
+👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
+We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -5201,7 +5283,7 @@
       </c>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919820012210?text=Hi%21%20Your%20website%20for%20Crox%20Lifestyle%20Systems%20looks%20a%20bit%20outdated%2C%20and%20I%20noticed%20it%27s%20not%20secure%20%28HTTPS%29.%0A%0AWe%20help%20CCTV%20companies%20like%20yours%20get%20more%20direct%20customer%20inquiries%20via%20a%20modern%20website%20with%20instant%20WhatsApp%20quotes.%0A%0ASee%20a%20LIVE%20DEMO%3A%20https%3A//atryasolutions.netlify.app/%0A%0AWant%20a%20quick%2010-15%20min%20chat%20to%20explore%20a%20free%20revamp%3F</t>
+          <t>https://wa.me/919820012210?text=Hi%20Crox%20Lifestyle%20Systems%2C%0ATook%20a%20look%20at%20your%20website%20in%20Mumbai.%20You%20have%20great%20reviews%2C%20but%20the%20site%20is%20missing%201-click%20WhatsApp%20quote%20buttons%20and%20mobile%20optimization%20%28not%20served%20over%20HTTPS%20%28insecure%20connection%29%3B%20no%20direct%20WhatsApp%20contact%20widget%3B%20outdated%20footer%20copyright%20%282018%29%29.%0A%0ACheck%20how%20modern%20CCTV%20sites%20convert%20mobile%20visitors%3A%20https%3A//atryasolutions.netlify.app/%0AWe%20also%20provide%20an%20AMC%20technician%20management%20panel%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T25" s="4" t="inlineStr">
@@ -5299,24 +5381,28 @@
       </c>
       <c r="AO25" s="4" t="inlineStr">
         <is>
-          <t>Hi! Your website for Crox Lifestyle Systems looks a bit outdated, and I noticed it's not secure (HTTPS).
-We help CCTV companies like yours get more direct customer inquiries via a modern website with instant WhatsApp quotes.
-See a LIVE DEMO: https://atryasolutions.netlify.app/
-Want a quick 10-15 min chat to explore a free revamp?</t>
+          <t>Hi Crox Lifestyle Systems,
+Took a look at your website in Mumbai. You have great reviews, but the site is missing 1-click WhatsApp quote buttons and mobile optimization (not served over HTTPS (insecure connection); no direct WhatsApp contact widget; outdated footer copyright (2018)).
+Check how modern CCTV sites convert mobile visitors: https://atryasolutions.netlify.app/
+We also provide an AMC technician management panel: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP25" s="4" t="inlineStr">
         <is>
-          <t>Boost Crox Lifestyle's Customer Inquiries</t>
+          <t>Upgrading customer quote conversion for Crox Lifestyle Systems</t>
         </is>
       </c>
       <c r="AQ25" s="4" t="inlineStr">
         <is>
-          <t>Dear Crox Lifestyle Systems Team,
-I noticed your website isn't served over HTTPS and lacks a direct WhatsApp contact, potentially losing you direct customer inquiries.
-At Atrya Solutions, we build modern, secure websites for CCTV companies with instant WhatsApp quote buttons to capture direct Google customers. This boosts leads and reduces reliance on commissions.
-See a LIVE DEMO of what we customize and launch for CCTV companies here: https://atryasolutions.netlify.app/
-Would you be open to a quick 10-15 minute walkthrough to see how we can revamp your online presence?
+          <t>Hi Crox Lifestyle Systems Team,
+I checked out your website while researching CCTV providers in Mumbai. You have solid customer ratings, but the site could capture significantly more inquiries with a direct WhatsApp quote widget and mobile lead forms (not served over HTTPS (insecure connection); no direct WhatsApp contact widget; outdated footer copyright (2018)).
+We build high-converting setups specifically for security installers:
+👉 Customer Website Demo: https://atryasolutions.netlify.app/
+👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see the upgrade?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -5415,7 +5501,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919550727878?text=Hi%20from%20Atrya%20Solutions%21%20Your%20Rtech%20Security%20website%20looks%20outdated%20and%20lacks%20a%20WhatsApp%20quote%20button.%20We%20build%20modern%20sites%20that%20capture%20direct%20Google%20customers%2C%20helping%20you%20avoid%20hefty%20commissions.%20See%20our%20LIVE%20DEMO%3A%20https%3A//atryasolutions.netlify.app/%0A%0AWant%20to%20see%20how%20we%20can%20boost%20your%20direct%20inquiries%3F%20Let%27s%20connect%20for%20a%20quick%2015-min%20chat.</t>
+          <t>https://wa.me/919550727878?text=Hi%20Rtech%20Security%20Solutions%2C%0ATook%20a%20look%20at%20your%20website%20in%20Chintalkunta.%20You%20have%20great%20reviews%2C%20but%20the%20site%20is%20missing%201-click%20WhatsApp%20quote%20buttons%20and%20mobile%20optimization%20%28not%20served%20over%20HTTPS%20%28insecure%20connection%29%3B%20no%20online%20enquiry%20or%20quote%20form%29.%0A%0ACheck%20how%20modern%20CCTV%20sites%20convert%20mobile%20visitors%3A%20https%3A//atryasolutions.netlify.app/%0AWe%20also%20provide%20an%20AMC%20technician%20management%20panel%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -5501,22 +5587,28 @@
       <c r="AN26" s="2" t="inlineStr"/>
       <c r="AO26" s="2" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions! Your Rtech Security website looks outdated and lacks a WhatsApp quote button. We build modern sites that capture direct Google customers, helping you avoid hefty commissions. See our LIVE DEMO: https://atryasolutions.netlify.app/
-Want to see how we can boost your direct inquiries? Let's connect for a quick 15-min chat.</t>
+          <t>Hi Rtech Security Solutions,
+Took a look at your website in Chintalkunta. You have great reviews, but the site is missing 1-click WhatsApp quote buttons and mobile optimization (not served over HTTPS (insecure connection); no online enquiry or quote form).
+Check how modern CCTV sites convert mobile visitors: https://atryasolutions.netlify.app/
+We also provide an AMC technician management panel: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP26" s="2" t="inlineStr">
         <is>
-          <t>Boost Rtech's Customer Enquiries &amp; Sales</t>
+          <t>Upgrading customer quote conversion for Rtech Security Solutions</t>
         </is>
       </c>
       <c r="AQ26" s="2" t="inlineStr">
         <is>
-          <t>Dear Rtech Security Solutions Team,
-I noticed your current website could be significantly more effective at capturing direct customer inquiries. An outdated site with no WhatsApp quote widget means missed opportunities from potential Google customers.
-We specialize in building high-converting websites for security companies, complete with instant WhatsApp quote buttons. This helps you get direct leads and reduce reliance on commission-based directories.
-See a LIVE DEMO of what we customize and launch: https://atryasolutions.netlify.app/
-Would you be open to a brief 10-15 minute walkthrough to show how we can boost your direct customer enquiries?
+          <t>Hi Rtech Security Solutions Team,
+I checked out your website while researching CCTV providers in Chintalkunta. You have solid customer ratings, but the site could capture significantly more inquiries with a direct WhatsApp quote widget and mobile lead forms (not served over HTTPS (insecure connection); no online enquiry or quote form).
+We build high-converting setups specifically for security installers:
+👉 Customer Website Demo: https://atryasolutions.netlify.app/
+👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see the upgrade?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -5701,24 +5793,28 @@
       </c>
       <c r="AO27" s="4" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions! Your website is missing a crucial element: a direct WhatsApp quote widget.
-Imagine capturing instant customer inquiries directly from Google, instead of losing them to competitors or paying commissions.
-We build modern websites with 1-click WhatsApp buttons, like this LIVE DEMO: https://atryasolutions.netlify.app/
-Boost your direct leads. Let's chat for 10 mins?</t>
+          <t>Hi Mahaveer Traders,
+Took a look at your website in Bengaluru. You have great reviews, but the site is missing 1-click WhatsApp quote buttons and mobile optimization (no online enquiry or quote form; no direct WhatsApp contact widget; outdated footer copyright (2015)).
+Check how modern CCTV sites convert mobile visitors: https://atryasolutions.netlify.app/
+We also provide an AMC technician management panel: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP27" s="4" t="inlineStr">
         <is>
-          <t>Boost Mahaveer Traders' Customer Enquiries</t>
+          <t>Upgrading customer quote conversion for Mahaveer Traders</t>
         </is>
       </c>
       <c r="AQ27" s="4" t="inlineStr">
         <is>
-          <t>Dear Mahaveer Traders Team,
-Your website has great potential, but it's missing key features to capture direct customer enquiries. A modern WhatsApp quote widget can instantly convert visitors into leads, bypassing commissions and outdated forms.
-See how we transform customer engagement with our LIVE DEMO: https://atryasolutions.netlify.app/
-We also offer an Operations &amp; AMC Dispatch Admin panel to streamline your field technicians: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-15 minute walkthrough to show you how we can boost your direct leads and automate operations?
+          <t>Hi Mahaveer Traders Team,
+I checked out your website while researching CCTV providers in Bengaluru. You have solid customer ratings, but the site could capture significantly more inquiries with a direct WhatsApp quote widget and mobile lead forms (no online enquiry or quote form; no direct WhatsApp contact widget; outdated footer copyright (2015)).
+We build high-converting setups specifically for security installers:
+👉 Customer Website Demo: https://atryasolutions.netlify.app/
+👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see the upgrade?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -5817,7 +5913,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/918151000777?text=Hi%20from%20Atrya%20Solutions%21%20Your%20website%2C%20cctvblr.com%2C%20looks%20a%20bit%20outdated.%20We%20can%20help%20you%20boost%20customer%20inquiries%20with%20a%20modern%20site%20featuring%20instant%20WhatsApp%20quote%20buttons.%20Get%20more%20direct%20leads%20and%20streamline%20your%20operations.%20Let%27s%20chat%20for%2010-15%20mins%3F</t>
+          <t>https://wa.me/918151000777?text=Hi%20Sky%20Systems%2C%0ATook%20a%20look%20at%20your%20website%20in%20Bengaluru.%20You%20have%20great%20reviews%2C%20but%20the%20site%20is%20missing%201-click%20WhatsApp%20quote%20buttons%20and%20mobile%20optimization%20%28not%20served%20over%20HTTPS%20%28insecure%20connection%29%3B%20outdated%20footer%20copyright%20%282018%29%29.%0A%0ACheck%20how%20modern%20CCTV%20sites%20convert%20mobile%20visitors%3A%20https%3A//atryasolutions.netlify.app/%0AWe%20also%20provide%20an%20AMC%20technician%20management%20panel%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -5907,22 +6003,28 @@
       </c>
       <c r="AO28" s="2" t="inlineStr">
         <is>
-          <t>Hi from Atrya Solutions! Your website, cctvblr.com, looks a bit outdated. We can help you boost customer inquiries with a modern site featuring instant WhatsApp quote buttons. Get more direct leads and streamline your operations. Let's chat for 10-15 mins?</t>
+          <t>Hi Sky Systems,
+Took a look at your website in Bengaluru. You have great reviews, but the site is missing 1-click WhatsApp quote buttons and mobile optimization (not served over HTTPS (insecure connection); outdated footer copyright (2018)).
+Check how modern CCTV sites convert mobile visitors: https://atryasolutions.netlify.app/
+We also provide an AMC technician management panel: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP28" s="2" t="inlineStr">
         <is>
-          <t>Boost Sky Systems' Customer Inquiries &amp; Efficiency</t>
+          <t>Upgrading customer quote conversion for Sky Systems</t>
         </is>
       </c>
       <c r="AQ28" s="2" t="inlineStr">
         <is>
-          <t>Dear Sky Systems Team,
-I noticed your website, cctvblr.com, could use a refresh. An outdated site often means missed customer inquiries.
-At Atrya Solutions, we build modern, high-converting websites for CCTV companies like yours, featuring instant WhatsApp quote buttons to capture direct Google customers.
-See a LIVE DEMO of what we customize: https://atryasolutions.netlify.app/
-We also offer an Operations &amp; AMC Dispatch Admin Panel: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-15 minute walkthrough to show you how we can boost your leads and streamline operations?
+          <t>Hi Sky Systems Team,
+I checked out your website while researching CCTV providers in Bengaluru. You have solid customer ratings, but the site could capture significantly more inquiries with a direct WhatsApp quote widget and mobile lead forms (not served over HTTPS (insecure connection); outdated footer copyright (2018)).
+We build high-converting setups specifically for security installers:
+👉 Customer Website Demo: https://atryasolutions.netlify.app/
+👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see the upgrade?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -6021,7 +6123,7 @@
       </c>
       <c r="S29" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919611444440?text=Hi%20Safetron%20Technologies%2C%0AYour%20site%20still%20shows%20a%202013%20footer%20and%20lacks%20any%20direct%20quote%20form%E2%80%94meaning%20missed%20Google%20leads.%20We%20can%20replace%20it%20with%20a%20modern%2C%20high%E2%80%91converting%20website%20featuring%201%E2%80%91click%20WhatsApp%20quote%20buttons%20and%20lead%20forms.%0ASee%20a%20LIVE%20DEMO%3A%20https%3A//atryasolutions.netlify.app/%0AAdmin%20panel%20demo%3A%20https%3A//atryasolutions.netlify.app/admin%0ACan%20we%20schedule%20a%2010%E2%80%91min%20walkthrough%3F</t>
+          <t>https://wa.me/919611444440?text=Hi%20Safetron%20Technologies%20Pvt%20Ltd%2C%0ATook%20a%20look%20at%20your%20website%20in%20Bengaluru.%20You%20have%20great%20reviews%2C%20but%20the%20site%20is%20missing%201-click%20WhatsApp%20quote%20buttons%20and%20mobile%20optimization%20%28no%20online%20enquiry%20or%20quote%20form%3B%20outdated%20footer%20copyright%20%282013%29%29.%0A%0ACheck%20how%20modern%20CCTV%20sites%20convert%20mobile%20visitors%3A%20https%3A//atryasolutions.netlify.app/%0AWe%20also%20provide%20an%20AMC%20technician%20management%20panel%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T29" s="4" t="inlineStr">
@@ -6111,24 +6213,28 @@
       </c>
       <c r="AO29" s="4" t="inlineStr">
         <is>
-          <t>Hi Safetron Technologies,
-Your site still shows a 2013 footer and lacks any direct quote form—meaning missed Google leads. We can replace it with a modern, high‑converting website featuring 1‑click WhatsApp quote buttons and lead forms.
-See a LIVE DEMO: https://atryasolutions.netlify.app/
-Admin panel demo: https://atryasolutions.netlify.app/admin
-Can we schedule a 10‑min walkthrough?</t>
+          <t>Hi Safetron Technologies Pvt Ltd,
+Took a look at your website in Bengaluru. You have great reviews, but the site is missing 1-click WhatsApp quote buttons and mobile optimization (no online enquiry or quote form; outdated footer copyright (2013)).
+Check how modern CCTV sites convert mobile visitors: https://atryasolutions.netlify.app/
+We also provide an AMC technician management panel: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP29" s="4" t="inlineStr">
         <is>
-          <t>Boost Leads with WhatsApp Quotes</t>
+          <t>Upgrading customer quote conversion for Safetron Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="AQ29" s="4" t="inlineStr">
         <is>
-          <t>Hi Safetron Technologies,
-I noticed your website still carries a 2013 footer and has no online enquiry or quote form. That means you’re losing direct Google customers to competitors who capture leads instantly.
-Atrya Solutions can revamp your site into a high‑converting, mobile‑ready platform with a 1‑click WhatsApp quote button and custom lead forms—turning every search visitor into a qualified lead. Our LIVE DEMO (https://atryasolutions.netlify.app/) shows exactly what we’ll build, and the Operations &amp; AMC Dispatch Admin (https://atryasolutions.netlify.app/admin) streamlines technician scheduling and service renewals.
-Would you have 10‑15 minutes for a quick walkthrough?
+          <t>Hi Safetron Technologies Pvt Ltd Team,
+I checked out your website while researching CCTV providers in Bengaluru. You have solid customer ratings, but the site could capture significantly more inquiries with a direct WhatsApp quote widget and mobile lead forms (no online enquiry or quote form; outdated footer copyright (2013)).
+We build high-converting setups specifically for security installers:
+👉 Customer Website Demo: https://atryasolutions.netlify.app/
+👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see the upgrade?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -6298,24 +6404,27 @@
       <c r="AO30" s="2" t="inlineStr">
         <is>
           <t>Hi Dahua wiki,
-Took a look at your CCTV website in Keralam and noticed a few things holding back customer enquiries (slow load time (6.0s); no direct WhatsApp contact widget).
-We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
-Open to a quick demo?</t>
+Took a look at your website in Keralam. You have great reviews, but the site is missing 1-click WhatsApp quote buttons and mobile optimization (slow load time (6.0s); no direct WhatsApp contact widget).
+Check how modern CCTV sites convert mobile visitors: https://atryasolutions.netlify.app/
+We also provide an AMC technician management panel: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP30" s="2" t="inlineStr">
         <is>
-          <t>Improving CCTV quote enquiries for Dahua wiki</t>
+          <t>Upgrading customer quote conversion for Dahua wiki</t>
         </is>
       </c>
       <c r="AQ30" s="2" t="inlineStr">
         <is>
-          <t>Hi Dahua wiki,
-I was looking up CCTV providers in Keralam and checked your website.
-I noticed a couple of areas that might be reducing your lead conversion: slow load time (6.0s); no direct WhatsApp contact widget.
-At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
-Live demo: https://atryasolutions.netlify.app/
-Would you be interested in a brief 10-minute walkthrough?
+          <t>Hi Dahua wiki Team,
+I checked out your website while researching CCTV providers in Keralam. You have solid customer ratings, but the site could capture significantly more inquiries with a direct WhatsApp quote widget and mobile lead forms (slow load time (6.0s); no direct WhatsApp contact widget).
+We build high-converting setups specifically for security installers:
+👉 Customer Website Demo: https://atryasolutions.netlify.app/
+👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see the upgrade?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -6414,7 +6523,7 @@
       </c>
       <c r="S31" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919110421987?text=Hi%20I%20Pro%20Secure%20CCTV%20CAMERA%20INSTALLATION%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%20Bengaluru%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+          <t>https://wa.me/919110421987?text=Hi%20I%20Pro%20Secure%20CCTV%20CAMERA%20INSTALLATION%2C%0ATook%20a%20look%20at%20your%20website%20in%20Bengaluru.%20You%20have%20great%20reviews%2C%20but%20the%20site%20is%20missing%201-click%20WhatsApp%20quote%20buttons%20and%20mobile%20optimization%20%28no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0A%0ACheck%20how%20modern%20CCTV%20sites%20convert%20mobile%20visitors%3A%20https%3A//atryasolutions.netlify.app/%0AWe%20also%20provide%20an%20AMC%20technician%20management%20panel%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T31" s="4" t="inlineStr"/>
@@ -6497,24 +6606,27 @@
       <c r="AO31" s="4" t="inlineStr">
         <is>
           <t>Hi I Pro Secure CCTV CAMERA INSTALLATION,
-Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (no online enquiry or quote form; no direct WhatsApp contact widget).
-We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
-Open to a quick demo?</t>
+Took a look at your website in Bengaluru. You have great reviews, but the site is missing 1-click WhatsApp quote buttons and mobile optimization (no online enquiry or quote form; no direct WhatsApp contact widget).
+Check how modern CCTV sites convert mobile visitors: https://atryasolutions.netlify.app/
+We also provide an AMC technician management panel: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP31" s="4" t="inlineStr">
         <is>
-          <t>Improving CCTV quote enquiries for I Pro Secure CCTV CAMERA INSTALLATION</t>
+          <t>Upgrading customer quote conversion for I Pro Secure CCTV CAMERA INSTALLATION</t>
         </is>
       </c>
       <c r="AQ31" s="4" t="inlineStr">
         <is>
-          <t>Hi I Pro Secure CCTV CAMERA INSTALLATION,
-I was looking up CCTV providers in Bengaluru and checked your website.
-I noticed a couple of areas that might be reducing your lead conversion: no online enquiry or quote form; no direct WhatsApp contact widget.
-At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
-Live demo: https://atryasolutions.netlify.app/
-Would you be interested in a brief 10-minute walkthrough?
+          <t>Hi I Pro Secure CCTV CAMERA INSTALLATION Team,
+I checked out your website while researching CCTV providers in Bengaluru. You have solid customer ratings, but the site could capture significantly more inquiries with a direct WhatsApp quote widget and mobile lead forms (no online enquiry or quote form; no direct WhatsApp contact widget).
+We build high-converting setups specifically for security installers:
+👉 Customer Website Demo: https://atryasolutions.netlify.app/
+👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see the upgrade?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -6613,7 +6725,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919741427427?text=Hi%20RAMESH%20CCTV%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%20Bengaluru%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+          <t>https://wa.me/919741427427?text=Hi%20RAMESH%20CCTV%2C%0ATook%20a%20look%20at%20your%20website%20in%20Bengaluru.%20You%20have%20great%20reviews%2C%20but%20the%20site%20is%20missing%201-click%20WhatsApp%20quote%20buttons%20and%20mobile%20optimization%20%28no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0A%0ACheck%20how%20modern%20CCTV%20sites%20convert%20mobile%20visitors%3A%20https%3A//atryasolutions.netlify.app/%0AWe%20also%20provide%20an%20AMC%20technician%20management%20panel%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -6700,24 +6812,27 @@
       <c r="AO32" s="2" t="inlineStr">
         <is>
           <t>Hi RAMESH CCTV,
-Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (no online enquiry or quote form; no direct WhatsApp contact widget).
-We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
-Open to a quick demo?</t>
+Took a look at your website in Bengaluru. You have great reviews, but the site is missing 1-click WhatsApp quote buttons and mobile optimization (no online enquiry or quote form; no direct WhatsApp contact widget).
+Check how modern CCTV sites convert mobile visitors: https://atryasolutions.netlify.app/
+We also provide an AMC technician management panel: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP32" s="2" t="inlineStr">
         <is>
-          <t>Improving CCTV quote enquiries for RAMESH CCTV</t>
+          <t>Upgrading customer quote conversion for RAMESH CCTV</t>
         </is>
       </c>
       <c r="AQ32" s="2" t="inlineStr">
         <is>
-          <t>Hi RAMESH CCTV,
-I was looking up CCTV providers in Bengaluru and checked your website.
-I noticed a couple of areas that might be reducing your lead conversion: no online enquiry or quote form; no direct WhatsApp contact widget.
-At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
-Live demo: https://atryasolutions.netlify.app/
-Would you be interested in a brief 10-minute walkthrough?
+          <t>Hi RAMESH CCTV Team,
+I checked out your website while researching CCTV providers in Bengaluru. You have solid customer ratings, but the site could capture significantly more inquiries with a direct WhatsApp quote widget and mobile lead forms (no online enquiry or quote form; no direct WhatsApp contact widget).
+We build high-converting setups specifically for security installers:
+👉 Customer Website Demo: https://atryasolutions.netlify.app/
+👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see the upgrade?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -6816,7 +6931,7 @@
       </c>
       <c r="S33" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919035080007?text=Hi%20SIXAXIS%20CCTV%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%20Bengaluru%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28not%20served%20over%20HTTPS%20%28insecure%20connection%29%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+          <t>https://wa.me/919035080007?text=Hi%20SIXAXIS%20CCTV%2C%0ATook%20a%20look%20at%20your%20website%20in%20Bengaluru.%20You%20have%20great%20reviews%2C%20but%20the%20site%20is%20missing%201-click%20WhatsApp%20quote%20buttons%20and%20mobile%20optimization%20%28not%20served%20over%20HTTPS%20%28insecure%20connection%29%29.%0A%0ACheck%20how%20modern%20CCTV%20sites%20convert%20mobile%20visitors%3A%20https%3A//atryasolutions.netlify.app/%0AWe%20also%20provide%20an%20AMC%20technician%20management%20panel%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T33" s="4" t="inlineStr">
@@ -6923,24 +7038,27 @@
       <c r="AO33" s="4" t="inlineStr">
         <is>
           <t>Hi SIXAXIS CCTV,
-Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (not served over HTTPS (insecure connection)).
-We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
-Open to a quick demo?</t>
+Took a look at your website in Bengaluru. You have great reviews, but the site is missing 1-click WhatsApp quote buttons and mobile optimization (not served over HTTPS (insecure connection)).
+Check how modern CCTV sites convert mobile visitors: https://atryasolutions.netlify.app/
+We also provide an AMC technician management panel: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP33" s="4" t="inlineStr">
         <is>
-          <t>Improving CCTV quote enquiries for SIXAXIS CCTV</t>
+          <t>Upgrading customer quote conversion for SIXAXIS CCTV</t>
         </is>
       </c>
       <c r="AQ33" s="4" t="inlineStr">
         <is>
-          <t>Hi SIXAXIS CCTV,
-I was looking up CCTV providers in Bengaluru and checked your website.
-I noticed a couple of areas that might be reducing your lead conversion: not served over HTTPS (insecure connection).
-At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
-Live demo: https://atryasolutions.netlify.app/
-Would you be interested in a brief 10-minute walkthrough?
+          <t>Hi SIXAXIS CCTV Team,
+I checked out your website while researching CCTV providers in Bengaluru. You have solid customer ratings, but the site could capture significantly more inquiries with a direct WhatsApp quote widget and mobile lead forms (not served over HTTPS (insecure connection)).
+We build high-converting setups specifically for security installers:
+👉 Customer Website Demo: https://atryasolutions.netlify.app/
+👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see the upgrade?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -7039,7 +7157,7 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919538380555?text=Hi%20CCTV%20SHOPPING%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%20Bengaluru%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+          <t>https://wa.me/919538380555?text=Hi%20CCTV%20SHOPPING%2C%0ATook%20a%20look%20at%20your%20website%20in%20Bengaluru.%20You%20have%20great%20reviews%2C%20but%20the%20site%20is%20missing%201-click%20WhatsApp%20quote%20buttons%20and%20mobile%20optimization%20%28no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0A%0ACheck%20how%20modern%20CCTV%20sites%20convert%20mobile%20visitors%3A%20https%3A//atryasolutions.netlify.app/%0AWe%20also%20provide%20an%20AMC%20technician%20management%20panel%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -7126,24 +7244,27 @@
       <c r="AO34" s="2" t="inlineStr">
         <is>
           <t>Hi CCTV SHOPPING,
-Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (no online enquiry or quote form; no direct WhatsApp contact widget).
-We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
-Open to a quick demo?</t>
+Took a look at your website in Bengaluru. You have great reviews, but the site is missing 1-click WhatsApp quote buttons and mobile optimization (no online enquiry or quote form; no direct WhatsApp contact widget).
+Check how modern CCTV sites convert mobile visitors: https://atryasolutions.netlify.app/
+We also provide an AMC technician management panel: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP34" s="2" t="inlineStr">
         <is>
-          <t>Improving CCTV quote enquiries for CCTV SHOPPING</t>
+          <t>Upgrading customer quote conversion for CCTV SHOPPING</t>
         </is>
       </c>
       <c r="AQ34" s="2" t="inlineStr">
         <is>
-          <t>Hi CCTV SHOPPING,
-I was looking up CCTV providers in Bengaluru and checked your website.
-I noticed a couple of areas that might be reducing your lead conversion: no online enquiry or quote form; no direct WhatsApp contact widget.
-At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
-Live demo: https://atryasolutions.netlify.app/
-Would you be interested in a brief 10-minute walkthrough?
+          <t>Hi CCTV SHOPPING Team,
+I checked out your website while researching CCTV providers in Bengaluru. You have solid customer ratings, but the site could capture significantly more inquiries with a direct WhatsApp quote widget and mobile lead forms (no online enquiry or quote form; no direct WhatsApp contact widget).
+We build high-converting setups specifically for security installers:
+👉 Customer Website Demo: https://atryasolutions.netlify.app/
+👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see the upgrade?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -7242,7 +7363,7 @@
       </c>
       <c r="S35" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919739933180?text=Hi%20KWALITY%20TECH%20ZONE%20LLP%2C%0ATook%20a%20look%20at%20your%20CCTV%20website%20in%20Bengaluru%20and%20noticed%20a%20few%20things%20holding%20back%20customer%20enquiries%20%28no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0AWe%20build%20modern%20sites%20with%20instant%20WhatsApp%20quote%20buttons%3A%20https%3A//atryasolutions.netlify.app/%0AOpen%20to%20a%20quick%20demo%3F</t>
+          <t>https://wa.me/919739933180?text=Hi%20KWALITY%20TECH%20ZONE%20LLP%2C%0ATook%20a%20look%20at%20your%20website%20in%20Bengaluru.%20You%20have%20great%20reviews%2C%20but%20the%20site%20is%20missing%201-click%20WhatsApp%20quote%20buttons%20and%20mobile%20optimization%20%28no%20online%20enquiry%20or%20quote%20form%3B%20no%20direct%20WhatsApp%20contact%20widget%29.%0A%0ACheck%20how%20modern%20CCTV%20sites%20convert%20mobile%20visitors%3A%20https%3A//atryasolutions.netlify.app/%0AWe%20also%20provide%20an%20AMC%20technician%20management%20panel%3A%20https%3A//atryasolutions.netlify.app/admin%0A%0AOpen%20for%20a%20quick%2010-min%20walkthrough%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T35" s="4" t="inlineStr"/>
@@ -7321,24 +7442,27 @@
       <c r="AO35" s="4" t="inlineStr">
         <is>
           <t>Hi KWALITY TECH ZONE LLP,
-Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (no online enquiry or quote form; no direct WhatsApp contact widget).
-We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
-Open to a quick demo?</t>
+Took a look at your website in Bengaluru. You have great reviews, but the site is missing 1-click WhatsApp quote buttons and mobile optimization (no online enquiry or quote form; no direct WhatsApp contact widget).
+Check how modern CCTV sites convert mobile visitors: https://atryasolutions.netlify.app/
+We also provide an AMC technician management panel: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP35" s="4" t="inlineStr">
         <is>
-          <t>Improving CCTV quote enquiries for KWALITY TECH ZONE LLP</t>
+          <t>Upgrading customer quote conversion for KWALITY TECH ZONE LLP</t>
         </is>
       </c>
       <c r="AQ35" s="4" t="inlineStr">
         <is>
-          <t>Hi KWALITY TECH ZONE LLP,
-I was looking up CCTV providers in Bengaluru and checked your website.
-I noticed a couple of areas that might be reducing your lead conversion: no online enquiry or quote form; no direct WhatsApp contact widget.
-At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
-Live demo: https://atryasolutions.netlify.app/
-Would you be interested in a brief 10-minute walkthrough?
+          <t>Hi KWALITY TECH ZONE LLP Team,
+I checked out your website while researching CCTV providers in Bengaluru. You have solid customer ratings, but the site could capture significantly more inquiries with a direct WhatsApp quote widget and mobile lead forms (no online enquiry or quote form; no direct WhatsApp contact widget).
+We build high-converting setups specifically for security installers:
+👉 Customer Website Demo: https://atryasolutions.netlify.app/
+👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see the upgrade?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -7508,24 +7632,27 @@
       <c r="AO36" s="2" t="inlineStr">
         <is>
           <t>Hi Bangalore Electronics,
-Took a look at your CCTV website in Bengaluru and noticed a few things holding back customer enquiries (no online enquiry or quote form; no direct WhatsApp contact widget).
-We build modern sites with instant WhatsApp quote buttons: https://atryasolutions.netlify.app/
-Open to a quick demo?</t>
+Took a look at your website in Bengaluru. You have great reviews, but the site is missing 1-click WhatsApp quote buttons and mobile optimization (no online enquiry or quote form; no direct WhatsApp contact widget).
+Check how modern CCTV sites convert mobile visitors: https://atryasolutions.netlify.app/
+We also provide an AMC technician management panel: https://atryasolutions.netlify.app/admin
+Open for a quick 10-min walkthrough? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP36" s="2" t="inlineStr">
         <is>
-          <t>Improving CCTV quote enquiries for Bangalore Electronics</t>
+          <t>Upgrading customer quote conversion for Bangalore Electronics</t>
         </is>
       </c>
       <c r="AQ36" s="2" t="inlineStr">
         <is>
-          <t>Hi Bangalore Electronics,
-I was looking up CCTV providers in Bengaluru and checked your website.
-I noticed a couple of areas that might be reducing your lead conversion: no online enquiry or quote form; no direct WhatsApp contact widget.
-At Atrya Solutions, we build high-converting websites and AMC management systems for security installers.
-Live demo: https://atryasolutions.netlify.app/
-Would you be interested in a brief 10-minute walkthrough?
+          <t>Hi Bangalore Electronics Team,
+I checked out your website while researching CCTV providers in Bengaluru. You have solid customer ratings, but the site could capture significantly more inquiries with a direct WhatsApp quote widget and mobile lead forms (no online enquiry or quote form; no direct WhatsApp contact widget).
+We build high-converting setups specifically for security installers:
+👉 Customer Website Demo: https://atryasolutions.netlify.app/
+👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
+Would you be open to a quick 10-minute walkthrough to see the upgrade?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -7624,7 +7751,7 @@
       </c>
       <c r="S37" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919738966594?text=Hi%20Cyber%20Pro%20India%20-%20CCTV%20Installation%20Service%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/919738966594?text=Hi%20Cyber%20Pro%20India%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T37" s="4" t="inlineStr">
@@ -7730,24 +7857,28 @@
       </c>
       <c r="AO37" s="4" t="inlineStr">
         <is>
-          <t>Hi Cyber Pro India - CCTV Installation Service,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+          <t>Hi Cyber Pro India,
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP37" s="4" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for Cyber Pro India - CCTV Installation Service</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for Cyber Pro India</t>
         </is>
       </c>
       <c r="AQ37" s="4" t="inlineStr">
         <is>
-          <t>Hi Cyber Pro India - CCTV Installation Service,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi Cyber Pro India Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -7846,7 +7977,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919686550099?text=Hi%20Skafoss%20Technologies%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/919686550099?text=Hi%20Skafoss%20Technologies%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -7937,23 +8068,27 @@
       <c r="AO38" s="2" t="inlineStr">
         <is>
           <t>Hi Skafoss Technologies,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP38" s="2" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for Skafoss Technologies</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for Skafoss Technologies</t>
         </is>
       </c>
       <c r="AQ38" s="2" t="inlineStr">
         <is>
-          <t>Hi Skafoss Technologies,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi Skafoss Technologies Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -8052,7 +8187,7 @@
       </c>
       <c r="S39" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919620421001?text=Hi%20KING%20TECHNOLOGY%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/919620421001?text=Hi%20KING%20TECHNOLOGY%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T39" s="4" t="inlineStr">
@@ -8143,23 +8278,27 @@
       <c r="AO39" s="4" t="inlineStr">
         <is>
           <t>Hi KING TECHNOLOGY,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP39" s="4" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for KING TECHNOLOGY</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for KING TECHNOLOGY</t>
         </is>
       </c>
       <c r="AQ39" s="4" t="inlineStr">
         <is>
-          <t>Hi KING TECHNOLOGY,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi KING TECHNOLOGY Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -8258,7 +8397,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/918147148767?text=Hi%20MY%20DISTRIBUTOR%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/918147148767?text=Hi%20MY%20DISTRIBUTOR%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
@@ -8357,23 +8496,27 @@
       <c r="AO40" s="2" t="inlineStr">
         <is>
           <t>Hi MY DISTRIBUTOR,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP40" s="2" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for MY DISTRIBUTOR</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for MY DISTRIBUTOR</t>
         </is>
       </c>
       <c r="AQ40" s="2" t="inlineStr">
         <is>
-          <t>Hi MY DISTRIBUTOR,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi MY DISTRIBUTOR Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -8472,7 +8615,7 @@
       </c>
       <c r="S41" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919513533180?text=Hi%20CAMERA%20COUNTRY%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/919513533180?text=Hi%20CAMERA%20COUNTRY%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T41" s="4" t="inlineStr">
@@ -8571,23 +8714,27 @@
       <c r="AO41" s="4" t="inlineStr">
         <is>
           <t>Hi CAMERA COUNTRY,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP41" s="4" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for CAMERA COUNTRY</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for CAMERA COUNTRY</t>
         </is>
       </c>
       <c r="AQ41" s="4" t="inlineStr">
         <is>
-          <t>Hi CAMERA COUNTRY,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi CAMERA COUNTRY Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -8686,7 +8833,7 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/917353033399?text=Hi%20Star%20vision%20solutions%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/917353033399?text=Hi%20Star%20vision%20solutions%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -8777,23 +8924,27 @@
       <c r="AO42" s="2" t="inlineStr">
         <is>
           <t>Hi Star vision solutions,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP42" s="2" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for Star vision solutions</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for Star vision solutions</t>
         </is>
       </c>
       <c r="AQ42" s="2" t="inlineStr">
         <is>
-          <t>Hi Star vision solutions,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi Star vision solutions Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -8963,23 +9114,27 @@
       <c r="AO43" s="4" t="inlineStr">
         <is>
           <t>Hi VISION ZOOM SECURITY SYSTEMS,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP43" s="4" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for VISION ZOOM SECURITY SYSTEMS</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for VISION ZOOM SECURITY SYSTEMS</t>
         </is>
       </c>
       <c r="AQ43" s="4" t="inlineStr">
         <is>
-          <t>Hi VISION ZOOM SECURITY SYSTEMS,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi VISION ZOOM SECURITY SYSTEMS Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -9078,7 +9233,7 @@
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919686037552?text=Hi%20HM%20Security%20Solutions%20%28CCTV%20Sales%20%26%20Service%29%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/919686037552?text=Hi%20HM%20Security%20Solutions%20%28CCTV%20Sales%20%26%20Service%29%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -9165,23 +9320,27 @@
       <c r="AO44" s="2" t="inlineStr">
         <is>
           <t>Hi HM Security Solutions (CCTV Sales &amp; Service),
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP44" s="2" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for HM Security Solutions (CCTV Sales &amp; Service)</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for HM Security Solutions (CCTV Sales &amp; Service)</t>
         </is>
       </c>
       <c r="AQ44" s="2" t="inlineStr">
         <is>
-          <t>Hi HM Security Solutions (CCTV Sales &amp; Service),
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi HM Security Solutions (CCTV Sales &amp; Service) Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -9280,7 +9439,7 @@
       </c>
       <c r="S45" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/918618084202?text=Hi%20Bangalore%20It%20Hub%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/918618084202?text=Hi%20Bangalore%20It%20Hub%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T45" s="4" t="inlineStr">
@@ -9367,23 +9526,27 @@
       <c r="AO45" s="4" t="inlineStr">
         <is>
           <t>Hi Bangalore It Hub,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP45" s="4" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for Bangalore It Hub</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for Bangalore It Hub</t>
         </is>
       </c>
       <c r="AQ45" s="4" t="inlineStr">
         <is>
-          <t>Hi Bangalore It Hub,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi Bangalore It Hub Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -9482,7 +9645,7 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/918618682725?text=Hi%20Mayur%20Infotech%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/918618682725?text=Hi%20Mayur%20Infotech%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
@@ -9569,23 +9732,27 @@
       <c r="AO46" s="2" t="inlineStr">
         <is>
           <t>Hi Mayur Infotech,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP46" s="2" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for Mayur Infotech</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for Mayur Infotech</t>
         </is>
       </c>
       <c r="AQ46" s="2" t="inlineStr">
         <is>
-          <t>Hi Mayur Infotech,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi Mayur Infotech Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -9684,7 +9851,7 @@
       </c>
       <c r="S47" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919916161100?text=Hi%20Rajlaxmi%20infotech%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/919916161100?text=Hi%20Rajlaxmi%20infotech%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T47" s="4" t="inlineStr">
@@ -9771,23 +9938,27 @@
       <c r="AO47" s="4" t="inlineStr">
         <is>
           <t>Hi Rajlaxmi infotech,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP47" s="4" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for Rajlaxmi infotech</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for Rajlaxmi infotech</t>
         </is>
       </c>
       <c r="AQ47" s="4" t="inlineStr">
         <is>
-          <t>Hi Rajlaxmi infotech,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi Rajlaxmi infotech Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -9886,7 +10057,7 @@
       </c>
       <c r="S48" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/916239110669?text=Hi%20Web%20Plus%20Security%20System%2C%0ASaw%20your%20CCTV%20website%20in%20Zirakpur.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/916239110669?text=Hi%20Web%20Plus%20Security%20System%2C%0ASaw%20your%20website%20in%20Zirakpur%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
@@ -9973,23 +10144,27 @@
       <c r="AO48" s="2" t="inlineStr">
         <is>
           <t>Hi Web Plus Security System,
-Saw your CCTV website in Zirakpur. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Zirakpur—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP48" s="2" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for Web Plus Security System</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for Web Plus Security System</t>
         </is>
       </c>
       <c r="AQ48" s="2" t="inlineStr">
         <is>
-          <t>Hi Web Plus Security System,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi Web Plus Security System Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -10088,7 +10263,7 @@
       </c>
       <c r="S49" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919035362143?text=Hi%20Yendra%20Techno%20Solution%20-%20CCTV%20Cameras%20Installation%20in%20Bengaluru%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/919035362143?text=Hi%20Yendra%20Techno%20Solution%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T49" s="4" t="inlineStr">
@@ -10174,24 +10349,28 @@
       <c r="AN49" s="4" t="inlineStr"/>
       <c r="AO49" s="4" t="inlineStr">
         <is>
-          <t>Hi Yendra Techno Solution - CCTV Cameras Installation in Bengaluru,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+          <t>Hi Yendra Techno Solution,
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP49" s="4" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for Yendra Techno Solution - CCTV Cameras Installation in Bengaluru</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for Yendra Techno Solution</t>
         </is>
       </c>
       <c r="AQ49" s="4" t="inlineStr">
         <is>
-          <t>Hi Yendra Techno Solution - CCTV Cameras Installation in Bengaluru,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi Yendra Techno Solution Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -10290,7 +10469,7 @@
       </c>
       <c r="S50" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/916361264243?text=Hi%20CCTV%20Surveillance%20Cameras%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/916361264243?text=Hi%20CCTV%20Surveillance%20Cameras%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
@@ -10385,23 +10564,27 @@
       <c r="AO50" s="2" t="inlineStr">
         <is>
           <t>Hi CCTV Surveillance Cameras,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP50" s="2" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for CCTV Surveillance Cameras</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for CCTV Surveillance Cameras</t>
         </is>
       </c>
       <c r="AQ50" s="2" t="inlineStr">
         <is>
-          <t>Hi CCTV Surveillance Cameras,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi CCTV Surveillance Cameras Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -10579,23 +10762,27 @@
       <c r="AO51" s="4" t="inlineStr">
         <is>
           <t>Hi MY COMPUTER AND CCTV ZONE,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP51" s="4" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for MY COMPUTER AND CCTV ZONE</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for MY COMPUTER AND CCTV ZONE</t>
         </is>
       </c>
       <c r="AQ51" s="4" t="inlineStr">
         <is>
-          <t>Hi MY COMPUTER AND CCTV ZONE,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi MY COMPUTER AND CCTV ZONE Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -10694,7 +10881,7 @@
       </c>
       <c r="S52" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/917026113516?text=Hi%20i2secure%20%E2%80%93%20Smart%20CCTV%20Solutions%20Bengaluru%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/917026113516?text=Hi%20i2secure%20%E2%80%93%20Smart%20CCTV%20Solutions%20Bengaluru%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
@@ -10777,23 +10964,27 @@
       <c r="AO52" s="2" t="inlineStr">
         <is>
           <t>Hi i2secure – Smart CCTV Solutions Bengaluru,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP52" s="2" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for i2secure – Smart CCTV Solutions Bengaluru</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for i2secure – Smart CCTV Solutions Bengaluru</t>
         </is>
       </c>
       <c r="AQ52" s="2" t="inlineStr">
         <is>
-          <t>Hi i2secure – Smart CCTV Solutions Bengaluru,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi i2secure – Smart CCTV Solutions Bengaluru Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -10892,7 +11083,7 @@
       </c>
       <c r="S53" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/918660317664?text=Hi%20Agasthya%20Electronics%20%7C%20CCTV%2C%20Solar%20Sim%20Cameras%2C%20Wi-Fi%20Cameras%2C%20Digital%20Door%20Locks%2C%20Video%20Door%20Phones%2C%20Access%20Control%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/918660317664?text=Hi%20Agasthya%20Electronics%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T53" s="4" t="inlineStr">
@@ -10998,24 +11189,28 @@
       </c>
       <c r="AO53" s="4" t="inlineStr">
         <is>
-          <t>Hi Agasthya Electronics | CCTV, Solar Sim Cameras, Wi-Fi Cameras, Digital Door Locks, Video Door Phones, Access Control,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+          <t>Hi Agasthya Electronics,
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP53" s="4" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for Agasthya Electronics | CCTV, Solar Sim Cameras, Wi-Fi Cameras, Digital Door Locks, Video Door Phones, Access Control</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for Agasthya Electronics</t>
         </is>
       </c>
       <c r="AQ53" s="4" t="inlineStr">
         <is>
-          <t>Hi Agasthya Electronics | CCTV, Solar Sim Cameras, Wi-Fi Cameras, Digital Door Locks, Video Door Phones, Access Control,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi Agasthya Electronics Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -11114,7 +11309,7 @@
       </c>
       <c r="S54" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919902234508?text=Hi%20CCTV%20ZONE%20IN%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/919902234508?text=Hi%20CCTV%20ZONE%20IN%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
@@ -11197,23 +11392,27 @@
       <c r="AO54" s="2" t="inlineStr">
         <is>
           <t>Hi CCTV ZONE IN,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP54" s="2" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for CCTV ZONE IN</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for CCTV ZONE IN</t>
         </is>
       </c>
       <c r="AQ54" s="2" t="inlineStr">
         <is>
-          <t>Hi CCTV ZONE IN,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi CCTV ZONE IN Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -11312,7 +11511,7 @@
       </c>
       <c r="S55" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919980040399?text=Hi%20MYF%20CCTV%20%26%20security%20systems%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/919980040399?text=Hi%20MYF%20CCTV%20%26%20security%20systems%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T55" s="4" t="inlineStr">
@@ -11399,23 +11598,27 @@
       <c r="AO55" s="4" t="inlineStr">
         <is>
           <t>Hi MYF CCTV &amp; security systems,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP55" s="4" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for MYF CCTV &amp; security systems</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for MYF CCTV &amp; security systems</t>
         </is>
       </c>
       <c r="AQ55" s="4" t="inlineStr">
         <is>
-          <t>Hi MYF CCTV &amp; security systems,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi MYF CCTV &amp; security systems Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -11514,7 +11717,7 @@
       </c>
       <c r="S56" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919739661248?text=Hi%20Computer%20IT%20Mart%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/919739661248?text=Hi%20Computer%20IT%20Mart%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
@@ -11613,23 +11816,27 @@
       <c r="AO56" s="2" t="inlineStr">
         <is>
           <t>Hi Computer IT Mart,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP56" s="2" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for Computer IT Mart</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for Computer IT Mart</t>
         </is>
       </c>
       <c r="AQ56" s="2" t="inlineStr">
         <is>
-          <t>Hi Computer IT Mart,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi Computer IT Mart Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -11728,7 +11935,7 @@
       </c>
       <c r="S57" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/917676954748?text=Hi%20Anvi%20Tech%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/917676954748?text=Hi%20Anvi%20Tech%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T57" s="4" t="inlineStr"/>
@@ -11807,23 +12014,27 @@
       <c r="AO57" s="4" t="inlineStr">
         <is>
           <t>Hi Anvi Tech,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP57" s="4" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for Anvi Tech</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for Anvi Tech</t>
         </is>
       </c>
       <c r="AQ57" s="4" t="inlineStr">
         <is>
-          <t>Hi Anvi Tech,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi Anvi Tech Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -11922,7 +12133,7 @@
       </c>
       <c r="S58" s="3" t="inlineStr">
         <is>
-          <t>https://wa.me/919353356153?text=Hi%20V-Tech%20-%20cctv%20cameras%20and%20installation%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/919353356153?text=Hi%20V-Tech%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
@@ -12004,24 +12215,28 @@
       <c r="AN58" s="2" t="inlineStr"/>
       <c r="AO58" s="2" t="inlineStr">
         <is>
-          <t>Hi V-Tech - cctv cameras and installation,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+          <t>Hi V-Tech,
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP58" s="2" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for V-Tech - cctv cameras and installation</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for V-Tech</t>
         </is>
       </c>
       <c r="AQ58" s="2" t="inlineStr">
         <is>
-          <t>Hi V-Tech - cctv cameras and installation,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi V-Tech Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -12120,7 +12335,7 @@
       </c>
       <c r="S59" s="5" t="inlineStr">
         <is>
-          <t>https://wa.me/919206979799?text=Hi%20CCTV%20Shield%20Care%2C%0ASaw%20your%20CCTV%20website%20in%20Bengaluru.%20How%20do%20you%20currently%20manage%20your%20AMC%20service%20renewals%20and%20technician%20dispatch%3F%0AWe%20built%20an%20operations%20panel%20specifically%20for%20security%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AWorth%20a%20quick%20look%3F</t>
+          <t>https://wa.me/919206979799?text=Hi%20CCTV%20Shield%20Care%2C%0ASaw%20your%20website%20in%20Bengaluru%E2%80%94looks%20solid%21%20How%20does%20your%20team%20currently%20manage%20annual%20maintenance%20contracts%20%28AMCs%29%2C%20warranty%20tracking%2C%20and%20technician%20dispatch%3F%0A%0AWe%20built%20a%20specialized%20operations%20panel%20for%20CCTV%20installers%3A%20https%3A//atryasolutions.netlify.app/admin%0AAutomates%20renewal%20alerts%20and%20job%20dispatch.%0A%0AWorth%20a%20quick%2010-min%20look%3F%20-%20Atrya%20Solutions</t>
         </is>
       </c>
       <c r="T59" s="4" t="inlineStr">
@@ -12207,23 +12422,27 @@
       <c r="AO59" s="4" t="inlineStr">
         <is>
           <t>Hi CCTV Shield Care,
-Saw your CCTV website in Bengaluru. How do you currently manage your AMC service renewals and technician dispatch?
-We built an operations panel specifically for security installers: https://atryasolutions.netlify.app/admin
-Worth a quick look?</t>
+Saw your website in Bengaluru—looks solid! How does your team currently manage annual maintenance contracts (AMCs), warranty tracking, and technician dispatch?
+We built a specialized operations panel for CCTV installers: https://atryasolutions.netlify.app/admin
+Automates renewal alerts and job dispatch.
+Worth a quick 10-min look? - Atrya Solutions</t>
         </is>
       </c>
       <c r="AP59" s="4" t="inlineStr">
         <is>
-          <t>AMC tracking &amp; technician panel for CCTV Shield Care</t>
+          <t>AMC Renewals &amp; Technician Dispatch Panel for CCTV Shield Care</t>
         </is>
       </c>
       <c r="AQ59" s="4" t="inlineStr">
         <is>
-          <t>Hi CCTV Shield Care,
-I came across your website and wanted to reach out.
-Most CCTV dealers tell us tracking annual maintenance contracts (AMCs), technician visits, and warranty renewals becomes chaotic on spreadsheets.
-We built a specialized operations panel for CCTV teams: https://atryasolutions.netlify.app/admin
-Would you be open to a quick 10-minute walkthrough to see if it saves your team time?
+          <t>Hi CCTV Shield Care Team,
+I came across your website and wanted to reach out. Your digital presence is well established!
+Most established security dealers tell us that as installation volume grows, tracking AMC maintenance renewals, warranty dates, and technician schedules on spreadsheets becomes chaotic.
+We built an operations panel specifically for CCTV and security teams: https://atryasolutions.netlify.app/admin
+It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
+Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
+Best regards,
+Atrya Solutions Team
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>

--- a/leads.xlsx
+++ b/leads.xlsx
@@ -922,7 +922,7 @@
 👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
 Could we connect for a brief 10-minute walkthrough this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1113,7 +1113,7 @@
 👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
 Could we connect for a brief 10-minute walkthrough this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1308,7 +1308,7 @@
 We customize and deliver the complete setup in 48 hours.
 Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1499,7 +1499,7 @@
 👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
 Could we connect for a brief 10-minute walkthrough this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1690,7 +1690,7 @@
 2. AMC Maintenance &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute demo to see how this brings direct inquiries without directory commissions?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -1881,7 +1881,7 @@
 👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
 Could we connect for a brief 10-minute walkthrough this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2076,7 +2076,7 @@
 We customize and deliver the complete setup in 48 hours.
 Would you be open to a brief 10-minute walkthrough this week to see how this can grow your direct inquiries?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2267,7 +2267,7 @@
 👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
 Could we connect for a brief 10-minute walkthrough this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2450,7 +2450,7 @@
 2. AMC Maintenance &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute demo to see how this brings direct inquiries without directory commissions?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2641,7 +2641,7 @@
 👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
 Could we connect for a brief 10-minute walkthrough this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -2832,7 +2832,7 @@
 👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
 Could we connect for a brief 10-minute walkthrough this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3011,7 +3011,7 @@
 👉 Warranty &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
 Could we connect for a brief 10-minute walkthrough this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3202,7 +3202,7 @@
 2. AMC Maintenance &amp; Technician Dispatch Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute demo to see how this brings direct inquiries without directory commissions?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3401,7 +3401,7 @@
 👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
 We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3592,7 +3592,7 @@
 👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
 We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3791,7 +3791,7 @@
 👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
 We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -3990,7 +3990,7 @@
 👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
 We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -4189,7 +4189,7 @@
 👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
 We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -4388,7 +4388,7 @@
 👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
 We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -4587,7 +4587,7 @@
 👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
 We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -4786,7 +4786,7 @@
 👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
 We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -4985,7 +4985,7 @@
 👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
 We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -5184,7 +5184,7 @@
 👉 Ops &amp; AMC Panel: https://atryasolutions.netlify.app/admin
 We'd love to offer a free revamp to get your digital presence fixed and capturing leads. Open for a brief 10-minute call this week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -5402,7 +5402,7 @@
 👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute walkthrough to see the upgrade?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -5608,7 +5608,7 @@
 👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute walkthrough to see the upgrade?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -5814,7 +5814,7 @@
 👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute walkthrough to see the upgrade?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -6024,7 +6024,7 @@
 👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute walkthrough to see the upgrade?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -6234,7 +6234,7 @@
 👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute walkthrough to see the upgrade?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -6424,7 +6424,7 @@
 👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute walkthrough to see the upgrade?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -6626,7 +6626,7 @@
 👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute walkthrough to see the upgrade?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -6832,7 +6832,7 @@
 👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute walkthrough to see the upgrade?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -7058,7 +7058,7 @@
 👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute walkthrough to see the upgrade?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -7264,7 +7264,7 @@
 👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute walkthrough to see the upgrade?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -7462,7 +7462,7 @@
 👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute walkthrough to see the upgrade?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -7652,7 +7652,7 @@
 👉 Technician &amp; AMC Renewal Admin: https://atryasolutions.netlify.app/admin
 Would you be open to a quick 10-minute walkthrough to see the upgrade?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -7878,7 +7878,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -8088,7 +8088,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -8298,7 +8298,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -8516,7 +8516,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -8734,7 +8734,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -8944,7 +8944,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -9134,7 +9134,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -9340,7 +9340,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -9546,7 +9546,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -9752,7 +9752,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -9958,7 +9958,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -10164,7 +10164,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -10370,7 +10370,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -10584,7 +10584,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -10782,7 +10782,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -10984,7 +10984,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -11210,7 +11210,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -11412,7 +11412,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -11618,7 +11618,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -11836,7 +11836,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -12034,7 +12034,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -12236,7 +12236,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
@@ -12442,7 +12442,7 @@
 It automates service reminders, tracks jobs, and keeps contract renewals on schedule.
 Would you be open to a quick 10-minute walkthrough to see if it saves your team hours every week?
 Best regards,
-Atrya Solutions Team
+Atrya Solutions (WhatsApp/Call: +919353489736)
 Reply STOP and I won't contact you again.</t>
         </is>
       </c>
